--- a/jogos_2025-05-30.xlsx
+++ b/jogos_2025-05-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
   <si>
     <t>Date</t>
   </si>
@@ -196,6 +196,9 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>12:30</t>
+  </si>
+  <si>
     <t>13:00</t>
   </si>
   <si>
@@ -247,18 +250,21 @@
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
+    <t>Croatia Druga HNL</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Norway First Division</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -298,19 +304,22 @@
     <t>Zhenys</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Yelimay Semey</t>
+    <t>GOŠK Gabela</t>
+  </si>
+  <si>
+    <t>Igman Konjic</t>
   </si>
   <si>
     <t>Aktobe</t>
   </si>
   <si>
-    <t>Igman Konjic</t>
-  </si>
-  <si>
-    <t>GOŠK Gabela</t>
+    <t>Bijelo Brdo</t>
   </si>
   <si>
     <t>Dinamo Brest</t>
@@ -319,45 +328,45 @@
     <t>Örebro</t>
   </si>
   <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Skeid</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Recoleta</t>
   </si>
   <si>
@@ -394,19 +403,22 @@
     <t>Ordabasy</t>
   </si>
   <si>
+    <t>Astana</t>
+  </si>
+  <si>
     <t>Atyrau</t>
   </si>
   <si>
-    <t>Astana</t>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
   </si>
   <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
+    <t>Dubrava Zagreb</t>
   </si>
   <si>
     <t>Isloch</t>
@@ -415,43 +427,43 @@
     <t>Brage</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
     <t>Hødd</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Sloboda Tuzla</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
     <t>Shelbourne</t>
   </si>
   <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
   </si>
   <si>
     <t>San Luis</t>
@@ -851,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD33"/>
+  <dimension ref="A1:BD34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -1032,16 +1044,16 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1056,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1131,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1202,16 +1214,16 @@
         <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1226,94 +1238,94 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1355,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="BB3">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BC3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD3" s="3">
         <v>45807.41666666666</v>
@@ -1369,19 +1381,19 @@
         <v>45807</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1396,94 +1408,94 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1525,13 +1537,13 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD4" s="3">
-        <v>45807.4375</v>
+        <v>45807.41666666666</v>
       </c>
     </row>
     <row r="5" spans="1:56">
@@ -1542,16 +1554,16 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1566,94 +1578,94 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1695,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD5" s="3">
         <v>45807.4375</v>
@@ -1712,16 +1724,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1736,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1811,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1882,16 +1894,16 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1906,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1981,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2055,13 +2067,13 @@
         <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2076,94 +2088,94 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK8" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2205,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD8" s="3">
         <v>45807.5</v>
@@ -2222,16 +2234,16 @@
         <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2246,25 +2258,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2297,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2321,10 +2333,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2375,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD9" s="3">
-        <v>45807.54166666666</v>
+        <v>45807.52083333334</v>
       </c>
     </row>
     <row r="10" spans="1:56">
@@ -2392,16 +2404,16 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2416,127 +2428,127 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L10">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="M10">
-        <v>3.23</v>
+        <v>3.18</v>
       </c>
       <c r="N10">
-        <v>2.62</v>
+        <v>4.14</v>
       </c>
       <c r="O10">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="P10">
-        <v>8.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q10">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="R10">
+        <v>1.31</v>
+      </c>
+      <c r="S10">
+        <v>3.04</v>
+      </c>
+      <c r="T10">
+        <v>2.57</v>
+      </c>
+      <c r="U10">
         <v>1.42</v>
       </c>
-      <c r="S10">
-        <v>2.75</v>
-      </c>
-      <c r="T10">
-        <v>2.9</v>
-      </c>
-      <c r="U10">
-        <v>1.36</v>
-      </c>
       <c r="V10">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AA10">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AD10">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE10">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="AI10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL10">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AM10">
         <v>1.28</v>
       </c>
       <c r="AN10">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2545,13 +2557,13 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="BC10">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="BD10" s="3">
-        <v>45807.58333333334</v>
+        <v>45807.54166666666</v>
       </c>
     </row>
     <row r="11" spans="1:56">
@@ -2559,19 +2571,19 @@
         <v>45807</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2586,127 +2598,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L11">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="M11">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="N11">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O11">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="P11">
         <v>8.5</v>
       </c>
       <c r="Q11">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="R11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="T11">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
         <v>1.36</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA11">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC11">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AD11">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="AE11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AH11">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AJ11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL11">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AM11">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AN11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR11">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AS11">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AT11">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AU11">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AV11">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AW11">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AX11">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AY11">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2715,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="BC11">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="BD11" s="3">
         <v>45807.58333333334</v>
@@ -2729,19 +2741,19 @@
         <v>45807</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2756,16 +2768,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L12">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="M12">
-        <v>5.9</v>
+        <v>5.29</v>
       </c>
       <c r="N12">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="O12">
         <v>1.17</v>
@@ -2777,64 +2789,64 @@
         <v>4.75</v>
       </c>
       <c r="R12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="T12">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="U12">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V12">
-        <v>4.55</v>
+        <v>4</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z12">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AA12">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AB12">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC12">
         <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE12">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF12">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AH12">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AI12">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AJ12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK12" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL12">
         <v>1.08</v>
@@ -2902,16 +2914,16 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2926,127 +2938,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK13" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3055,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD13" s="3">
-        <v>45807.625</v>
+        <v>45807.58333333334</v>
       </c>
     </row>
     <row r="14" spans="1:56">
@@ -3072,16 +3084,16 @@
         <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3096,127 +3108,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L14">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK14" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL14">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3225,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="BD14" s="3">
-        <v>45807.64583333334</v>
+        <v>45807.625</v>
       </c>
     </row>
     <row r="15" spans="1:56">
@@ -3242,16 +3254,16 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3266,127 +3278,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L15">
-        <v>3.76</v>
+        <v>1.81</v>
       </c>
       <c r="M15">
-        <v>3.11</v>
+        <v>3.8</v>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>3.95</v>
       </c>
       <c r="O15">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="P15">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q15">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="R15">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>2.37</v>
       </c>
       <c r="U15">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>2.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB15">
+        <v>1.65</v>
+      </c>
+      <c r="AC15">
+        <v>2.05</v>
+      </c>
+      <c r="AD15">
+        <v>2.6</v>
+      </c>
+      <c r="AE15">
+        <v>1.48</v>
+      </c>
+      <c r="AF15">
+        <v>1.6</v>
+      </c>
+      <c r="AG15">
         <v>2.2</v>
       </c>
-      <c r="AC15">
-        <v>1.55</v>
-      </c>
-      <c r="AD15">
-        <v>4.2</v>
-      </c>
-      <c r="AE15">
+      <c r="AH15">
+        <v>4.75</v>
+      </c>
+      <c r="AI15">
         <v>1.18</v>
       </c>
-      <c r="AF15">
-        <v>2.05</v>
-      </c>
-      <c r="AG15">
-        <v>1.7</v>
-      </c>
-      <c r="AH15">
-        <v>6.2</v>
-      </c>
-      <c r="AI15">
-        <v>1.06</v>
-      </c>
       <c r="AJ15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL15">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AM15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN15">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AR15">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AS15">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AT15">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AU15">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="AV15">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AW15">
         <v>1.78</v>
       </c>
       <c r="AX15">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AY15">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3395,13 +3407,13 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="BC15">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="BD15" s="3">
-        <v>45807.65625</v>
+        <v>45807.64583333334</v>
       </c>
     </row>
     <row r="16" spans="1:56">
@@ -3409,19 +3421,19 @@
         <v>45807</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3436,127 +3448,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L16">
-        <v>1.92</v>
+        <v>2.51</v>
       </c>
       <c r="M16">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="N16">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="O16">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="P16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R16">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="V16">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>7.75</v>
       </c>
       <c r="Z16">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AA16">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB16">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AD16">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
+        <v>1.85</v>
+      </c>
+      <c r="AG16">
+        <v>1.85</v>
+      </c>
+      <c r="AH16">
+        <v>8</v>
+      </c>
+      <c r="AI16">
+        <v>1.06</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL16">
         <v>1.33</v>
       </c>
-      <c r="AF16">
-        <v>1.73</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16">
-        <v>4.9</v>
-      </c>
-      <c r="AI16">
-        <v>1.13</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL16">
+      <c r="AM16">
         <v>1.3</v>
       </c>
-      <c r="AM16">
-        <v>1.22</v>
-      </c>
       <c r="AN16">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3565,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BC16">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="BD16" s="3">
         <v>45807.65625</v>
@@ -3579,19 +3591,19 @@
         <v>45807</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3606,52 +3618,52 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L17">
-        <v>2.51</v>
+        <v>1.96</v>
       </c>
       <c r="M17">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="N17">
-        <v>2.53</v>
+        <v>3.35</v>
       </c>
       <c r="O17">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="P17">
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="R17">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="T17">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V17">
         <v>7.5</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AA17">
         <v>2.9</v>
@@ -3660,73 +3672,73 @@
         <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AD17">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="AE17">
         <v>1.22</v>
       </c>
       <c r="AF17">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH17">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AI17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AJ17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK17" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL17">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AM17">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN17">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3735,10 +3747,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="BC17">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="BD17" s="3">
         <v>45807.65625</v>
@@ -3749,19 +3761,19 @@
         <v>45807</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3776,127 +3788,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L18">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="M18">
-        <v>3.47</v>
+        <v>3.11</v>
       </c>
       <c r="N18">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
         <v>2.75</v>
       </c>
       <c r="P18">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R18">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V18">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Z18">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AA18">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB18">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AD18">
-        <v>2.97</v>
+        <v>4.33</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AG18">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH18">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="AI18">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL18">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AM18">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AN18">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AQ18">
-        <v>1.56</v>
+        <v>1.71</v>
       </c>
       <c r="AR18">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AS18">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AT18">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="AU18">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AV18">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AW18">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AX18">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AY18">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3908,7 +3920,7 @@
         <v>2.75</v>
       </c>
       <c r="BC18">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BD18" s="3">
         <v>45807.65625</v>
@@ -3919,19 +3931,19 @@
         <v>45807</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3946,67 +3958,67 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L19">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="M19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N19">
         <v>3.8</v>
       </c>
       <c r="O19">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S19">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="U19">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V19">
         <v>6</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z19">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AA19">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD19">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AE19">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
@@ -4015,25 +4027,25 @@
         <v>2</v>
       </c>
       <c r="AH19">
-        <v>5.3</v>
+        <v>6.35</v>
       </c>
       <c r="AI19">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AJ19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL19">
         <v>1.25</v>
       </c>
       <c r="AM19">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AO19">
         <v>-1</v>
@@ -4075,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BC19">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="BD19" s="3">
         <v>45807.65625</v>
@@ -4089,19 +4101,19 @@
         <v>45807</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4116,94 +4128,94 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L20">
-        <v>1.96</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N20">
-        <v>3.35</v>
+        <v>1.54</v>
       </c>
       <c r="O20">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="R20">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S20">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U20">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="V20">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AA20">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC20">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AD20">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="AE20">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF20">
+        <v>1.8</v>
+      </c>
+      <c r="AG20">
         <v>1.85</v>
       </c>
-      <c r="AG20">
-        <v>1.8</v>
-      </c>
       <c r="AH20">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
       <c r="AI20">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AJ20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AM20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN20">
-        <v>1.77</v>
+        <v>1.13</v>
       </c>
       <c r="AO20">
         <v>-1</v>
@@ -4245,10 +4257,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="BC20">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="BD20" s="3">
         <v>45807.65625</v>
@@ -4259,19 +4271,19 @@
         <v>45807</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4286,127 +4298,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L21">
-        <v>2.47</v>
+        <v>1.79</v>
       </c>
       <c r="M21">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="O21">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q21">
+        <v>2.88</v>
+      </c>
+      <c r="R21">
+        <v>1.3</v>
+      </c>
+      <c r="S21">
+        <v>3.24</v>
+      </c>
+      <c r="T21">
+        <v>2.4</v>
+      </c>
+      <c r="U21">
+        <v>1.47</v>
+      </c>
+      <c r="V21">
+        <v>5.5</v>
+      </c>
+      <c r="W21">
+        <v>1.12</v>
+      </c>
+      <c r="X21">
+        <v>1.03</v>
+      </c>
+      <c r="Y21">
+        <v>10</v>
+      </c>
+      <c r="Z21">
+        <v>1.22</v>
+      </c>
+      <c r="AA21">
+        <v>4</v>
+      </c>
+      <c r="AB21">
+        <v>1.7</v>
+      </c>
+      <c r="AC21">
+        <v>1.95</v>
+      </c>
+      <c r="AD21">
+        <v>2.74</v>
+      </c>
+      <c r="AE21">
+        <v>1.4</v>
+      </c>
+      <c r="AF21">
+        <v>1.7</v>
+      </c>
+      <c r="AG21">
+        <v>2</v>
+      </c>
+      <c r="AH21">
+        <v>4.75</v>
+      </c>
+      <c r="AI21">
+        <v>1.15</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL21">
+        <v>1.25</v>
+      </c>
+      <c r="AM21">
+        <v>1.2</v>
+      </c>
+      <c r="AN21">
         <v>2.2</v>
-      </c>
-      <c r="R21">
-        <v>1.5</v>
-      </c>
-      <c r="S21">
-        <v>2.45</v>
-      </c>
-      <c r="T21">
-        <v>3.3</v>
-      </c>
-      <c r="U21">
-        <v>1.28</v>
-      </c>
-      <c r="V21">
-        <v>8.4</v>
-      </c>
-      <c r="W21">
-        <v>1.01</v>
-      </c>
-      <c r="X21">
-        <v>1.08</v>
-      </c>
-      <c r="Y21">
-        <v>6.5</v>
-      </c>
-      <c r="Z21">
-        <v>1.4</v>
-      </c>
-      <c r="AA21">
-        <v>2.7</v>
-      </c>
-      <c r="AB21">
-        <v>2.25</v>
-      </c>
-      <c r="AC21">
-        <v>1.53</v>
-      </c>
-      <c r="AD21">
-        <v>4.6</v>
-      </c>
-      <c r="AE21">
-        <v>1.18</v>
-      </c>
-      <c r="AF21">
-        <v>2</v>
-      </c>
-      <c r="AG21">
-        <v>1.75</v>
-      </c>
-      <c r="AH21">
-        <v>8.5</v>
-      </c>
-      <c r="AI21">
-        <v>1.05</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL21">
-        <v>1.36</v>
-      </c>
-      <c r="AM21">
-        <v>1.3</v>
-      </c>
-      <c r="AN21">
-        <v>1.5</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ21">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR21">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS21">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AT21">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU21">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV21">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW21">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX21">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY21">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4415,10 +4427,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="BC21">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="BD21" s="3">
         <v>45807.65625</v>
@@ -4429,19 +4441,19 @@
         <v>45807</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4456,127 +4468,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L22">
-        <v>1.81</v>
+        <v>2.47</v>
       </c>
       <c r="M22">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="N22">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
+        <v>1.91</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>2.2</v>
+      </c>
+      <c r="R22">
+        <v>1.48</v>
+      </c>
+      <c r="S22">
+        <v>2.45</v>
+      </c>
+      <c r="T22">
+        <v>3.3</v>
+      </c>
+      <c r="U22">
+        <v>1.28</v>
+      </c>
+      <c r="V22">
+        <v>8.4</v>
+      </c>
+      <c r="W22">
+        <v>1.01</v>
+      </c>
+      <c r="X22">
+        <v>1.04</v>
+      </c>
+      <c r="Y22">
+        <v>7</v>
+      </c>
+      <c r="Z22">
+        <v>1.41</v>
+      </c>
+      <c r="AA22">
+        <v>2.7</v>
+      </c>
+      <c r="AB22">
+        <v>2.25</v>
+      </c>
+      <c r="AC22">
         <v>1.53</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>2.75</v>
-      </c>
-      <c r="R22">
-        <v>1.32</v>
-      </c>
-      <c r="S22">
-        <v>2.95</v>
-      </c>
-      <c r="T22">
-        <v>2.8</v>
-      </c>
-      <c r="U22">
-        <v>1.4</v>
-      </c>
-      <c r="V22">
-        <v>6</v>
-      </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.05</v>
-      </c>
-      <c r="Y22">
-        <v>10</v>
-      </c>
-      <c r="Z22">
+      <c r="AD22">
+        <v>4.33</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
+        <v>2</v>
+      </c>
+      <c r="AG22">
+        <v>1.73</v>
+      </c>
+      <c r="AH22">
+        <v>8.4</v>
+      </c>
+      <c r="AI22">
+        <v>1.01</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL22">
+        <v>1.44</v>
+      </c>
+      <c r="AM22">
         <v>1.3</v>
       </c>
-      <c r="AA22">
-        <v>3.5</v>
-      </c>
-      <c r="AB22">
-        <v>1.87</v>
-      </c>
-      <c r="AC22">
-        <v>1.84</v>
-      </c>
-      <c r="AD22">
-        <v>3.14</v>
-      </c>
-      <c r="AE22">
-        <v>1.3</v>
-      </c>
-      <c r="AF22">
-        <v>1.67</v>
-      </c>
-      <c r="AG22">
-        <v>2</v>
-      </c>
-      <c r="AH22">
-        <v>5.5</v>
-      </c>
-      <c r="AI22">
-        <v>1.11</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL22">
-        <v>1.3</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
       <c r="AN22">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4585,10 +4597,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="BC22">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="BD22" s="3">
         <v>45807.65625</v>
@@ -4599,19 +4611,19 @@
         <v>45807</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4626,127 +4638,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L23">
-        <v>5</v>
+        <v>3.78</v>
       </c>
       <c r="M23">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N23">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P23">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q23">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="R23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S23">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="T23">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
         <v>1.42</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AB23">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC23">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD23">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AE23">
         <v>1.33</v>
       </c>
       <c r="AF23">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG23">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH23">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AI23">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL23">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="AM23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN23">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4755,10 +4767,10 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="BC23">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="BD23" s="3">
         <v>45807.65625</v>
@@ -4772,16 +4784,16 @@
         <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4796,94 +4808,94 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L24">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="M24">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N24">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
+        <v>1.5</v>
+      </c>
+      <c r="P24">
+        <v>9</v>
+      </c>
+      <c r="Q24">
+        <v>2.75</v>
+      </c>
+      <c r="R24">
+        <v>1.33</v>
+      </c>
+      <c r="S24">
+        <v>3.2</v>
+      </c>
+      <c r="T24">
+        <v>2.5</v>
+      </c>
+      <c r="U24">
+        <v>1.45</v>
+      </c>
+      <c r="V24">
+        <v>6.5</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>11</v>
+      </c>
+      <c r="Z24">
+        <v>1.24</v>
+      </c>
+      <c r="AA24">
+        <v>3.7</v>
+      </c>
+      <c r="AB24">
+        <v>1.73</v>
+      </c>
+      <c r="AC24">
         <v>1.91</v>
       </c>
-      <c r="P24">
-        <v>7</v>
-      </c>
-      <c r="Q24">
-        <v>2.3</v>
-      </c>
-      <c r="R24">
-        <v>1.49</v>
-      </c>
-      <c r="S24">
-        <v>2.4</v>
-      </c>
-      <c r="T24">
-        <v>3.34</v>
-      </c>
-      <c r="U24">
-        <v>1.29</v>
-      </c>
-      <c r="V24">
-        <v>8.5</v>
-      </c>
-      <c r="W24">
-        <v>1.04</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>6.8</v>
-      </c>
-      <c r="Z24">
-        <v>1.42</v>
-      </c>
-      <c r="AA24">
-        <v>2.62</v>
-      </c>
-      <c r="AB24">
-        <v>2.35</v>
-      </c>
-      <c r="AC24">
-        <v>1.57</v>
-      </c>
       <c r="AD24">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AF24">
+        <v>1.6</v>
+      </c>
+      <c r="AG24">
+        <v>2</v>
+      </c>
+      <c r="AH24">
+        <v>5.09</v>
+      </c>
+      <c r="AI24">
+        <v>1.11</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL24">
+        <v>1.25</v>
+      </c>
+      <c r="AM24">
+        <v>1.22</v>
+      </c>
+      <c r="AN24">
         <v>1.95</v>
-      </c>
-      <c r="AG24">
-        <v>1.75</v>
-      </c>
-      <c r="AH24">
-        <v>8.1</v>
-      </c>
-      <c r="AI24">
-        <v>1.04</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>157</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>157</v>
-      </c>
-      <c r="AL24">
-        <v>1.36</v>
-      </c>
-      <c r="AM24">
-        <v>1.31</v>
-      </c>
-      <c r="AN24">
-        <v>1.53</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -4925,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="BC24">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="BD24" s="3">
-        <v>45807.66666666666</v>
+        <v>45807.65625</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4939,19 +4951,19 @@
         <v>45807</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4966,139 +4978,139 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L25">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="M25">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N25">
-        <v>5.6</v>
+        <v>2.71</v>
       </c>
       <c r="O25">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="P25">
+        <v>7</v>
+      </c>
+      <c r="Q25">
+        <v>2.3</v>
+      </c>
+      <c r="R25">
+        <v>1.49</v>
+      </c>
+      <c r="S25">
+        <v>2.44</v>
+      </c>
+      <c r="T25">
+        <v>3.3</v>
+      </c>
+      <c r="U25">
+        <v>1.29</v>
+      </c>
+      <c r="V25">
         <v>8.5</v>
       </c>
-      <c r="Q25">
-        <v>3.5</v>
-      </c>
-      <c r="R25">
-        <v>1.4</v>
-      </c>
-      <c r="S25">
-        <v>2.64</v>
-      </c>
-      <c r="T25">
-        <v>2.9</v>
-      </c>
-      <c r="U25">
-        <v>1.35</v>
-      </c>
-      <c r="V25">
-        <v>7</v>
-      </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="Z25">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AA25">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC25">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD25">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="AE25">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG25">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH25">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AI25">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AJ25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL25">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AM25">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AN25">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR25">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
+      <c r="AV25">
+        <v>0</v>
+      </c>
+      <c r="AW25">
+        <v>0</v>
+      </c>
+      <c r="AX25">
+        <v>0</v>
+      </c>
+      <c r="AY25">
+        <v>0</v>
+      </c>
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+      <c r="BA25">
+        <v>0</v>
+      </c>
+      <c r="BB25">
+        <v>1.91</v>
+      </c>
+      <c r="BC25">
         <v>2.3</v>
-      </c>
-      <c r="AT25">
-        <v>2.95</v>
-      </c>
-      <c r="AU25">
-        <v>3.05</v>
-      </c>
-      <c r="AV25">
-        <v>2.32</v>
-      </c>
-      <c r="AW25">
-        <v>1.9</v>
-      </c>
-      <c r="AX25">
-        <v>1.52</v>
-      </c>
-      <c r="AY25">
-        <v>1.33</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>1.4</v>
-      </c>
-      <c r="BC25">
-        <v>3.5</v>
       </c>
       <c r="BD25" s="3">
         <v>45807.66666666666</v>
@@ -5112,16 +5124,16 @@
         <v>66</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5136,127 +5148,127 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5265,13 +5277,13 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BD26" s="3">
-        <v>45807.70833333334</v>
+        <v>45807.66666666666</v>
       </c>
     </row>
     <row r="27" spans="1:56">
@@ -5282,16 +5294,16 @@
         <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5306,127 +5318,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK27" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5435,13 +5447,13 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD27" s="3">
-        <v>45807.75</v>
+        <v>45807.70833333334</v>
       </c>
     </row>
     <row r="28" spans="1:56">
@@ -5452,16 +5464,16 @@
         <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5476,127 +5488,127 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L28">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK28" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO28">
         <v>-1</v>
       </c>
       <c r="AP28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5605,13 +5617,13 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD28" s="3">
-        <v>45807.79166666666</v>
+        <v>45807.75</v>
       </c>
     </row>
     <row r="29" spans="1:56">
@@ -5622,16 +5634,16 @@
         <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5646,127 +5658,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK29" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5775,13 +5787,13 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD29" s="3">
-        <v>45807.83333333334</v>
+        <v>45807.79166666666</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5792,16 +5804,16 @@
         <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F30" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5816,94 +5828,94 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L30">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M30">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK30" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL30">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AM30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN30">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO30">
         <v>-1</v>
@@ -5945,13 +5957,13 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BC30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD30" s="3">
-        <v>45807.875</v>
+        <v>45807.83333333334</v>
       </c>
     </row>
     <row r="31" spans="1:56">
@@ -5965,13 +5977,13 @@
         <v>86</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -5986,94 +5998,94 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ31" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK31" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO31">
         <v>-1</v>
@@ -6115,13 +6127,13 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD31" s="3">
-        <v>45807.89583333334</v>
+        <v>45807.875</v>
       </c>
     </row>
     <row r="32" spans="1:56">
@@ -6135,13 +6147,13 @@
         <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6156,127 +6168,127 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L32">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI32">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK32" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL32">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM32">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AN32">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO32">
         <v>-1</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AR32">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS32">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT32">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AU32">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AW32">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY32">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ32">
         <v>0</v>
@@ -6285,13 +6297,13 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BC32">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BD32" s="3">
-        <v>45807.91666666666</v>
+        <v>45807.89583333334</v>
       </c>
     </row>
     <row r="33" spans="1:56">
@@ -6302,16 +6314,16 @@
         <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6326,127 +6338,127 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="L33">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="M33">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="N33">
-        <v>2.18</v>
+        <v>3.07</v>
       </c>
       <c r="O33">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="R33">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="S33">
-        <v>3.75</v>
+        <v>2</v>
       </c>
       <c r="T33">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="U33">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="V33">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB33">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="AC33">
-        <v>2.37</v>
+        <v>1.28</v>
       </c>
       <c r="AD33">
-        <v>2.16</v>
+        <v>6.5</v>
       </c>
       <c r="AE33">
-        <v>1.61</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="AG33">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ33" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AK33" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AL33">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AM33">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO33">
         <v>-1</v>
       </c>
       <c r="AP33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV33">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AW33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY33">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -6455,12 +6467,182 @@
         <v>0</v>
       </c>
       <c r="BB33">
+        <v>1.83</v>
+      </c>
+      <c r="BC33">
+        <v>2.63</v>
+      </c>
+      <c r="BD33" s="3">
+        <v>45807.91666666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:56">
+      <c r="A34" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" t="s">
+        <v>159</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>160</v>
+      </c>
+      <c r="L34">
+        <v>2.7</v>
+      </c>
+      <c r="M34">
+        <v>3.55</v>
+      </c>
+      <c r="N34">
+        <v>2.18</v>
+      </c>
+      <c r="O34">
         <v>2.2</v>
       </c>
-      <c r="BC33">
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
         <v>1.73</v>
       </c>
-      <c r="BD33" s="3">
+      <c r="R34">
+        <v>1.25</v>
+      </c>
+      <c r="S34">
+        <v>3.75</v>
+      </c>
+      <c r="T34">
+        <v>2.2</v>
+      </c>
+      <c r="U34">
+        <v>1.62</v>
+      </c>
+      <c r="V34">
+        <v>4.5</v>
+      </c>
+      <c r="W34">
+        <v>1.17</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>1.53</v>
+      </c>
+      <c r="AC34">
+        <v>2.37</v>
+      </c>
+      <c r="AD34">
+        <v>2.16</v>
+      </c>
+      <c r="AE34">
+        <v>1.61</v>
+      </c>
+      <c r="AF34">
+        <v>1.53</v>
+      </c>
+      <c r="AG34">
+        <v>2.38</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AI34">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>161</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>0</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34">
+        <v>0</v>
+      </c>
+      <c r="AV34">
+        <v>0</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
+        <v>0</v>
+      </c>
+      <c r="BA34">
+        <v>0</v>
+      </c>
+      <c r="BB34">
+        <v>2.2</v>
+      </c>
+      <c r="BC34">
+        <v>1.73</v>
+      </c>
+      <c r="BD34" s="3">
         <v>45807.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-05-30.xlsx
+++ b/jogos_2025-05-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="172">
   <si>
     <t>Date</t>
   </si>
@@ -253,27 +253,33 @@
     <t>Croatia Druga HNL</t>
   </si>
   <si>
+    <t>Algeria Ligue 1</t>
+  </si>
+  <si>
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
+    <t>Turkey Süper Lig</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
+    <t>Republic of Ireland First Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland Premier Division</t>
   </si>
   <si>
-    <t>Republic of Ireland First Division</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -310,69 +316,81 @@
     <t>Tobol</t>
   </si>
   <si>
+    <t>Aktobe</t>
+  </si>
+  <si>
     <t>GOŠK Gabela</t>
   </si>
   <si>
     <t>Igman Konjic</t>
   </si>
   <si>
-    <t>Aktobe</t>
-  </si>
-  <si>
     <t>Bijelo Brdo</t>
   </si>
   <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Skeid</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Bohemians</t>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Sligo Rovers</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
+    <t>Shamrock Rovers</t>
   </si>
   <si>
     <t>Recoleta</t>
   </si>
   <si>
-    <t>Shamrock Rovers</t>
-  </si>
-  <si>
     <t>General Caballero JLM</t>
   </si>
   <si>
@@ -409,67 +427,79 @@
     <t>Atyrau</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Zrinjski</t>
   </si>
   <si>
     <t>Borac Banja Luka</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Isloch</t>
   </si>
   <si>
+    <t>İstanbul Başakşehir</t>
+  </si>
+  <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Hødd</t>
   </si>
   <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
     <t>Sloboda Tuzla</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
     <t>Drogheda United</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Derry City</t>
+    <t>Finn Harps</t>
   </si>
   <si>
     <t>St Patrick's Athl.</t>
   </si>
   <si>
-    <t>Finn Harps</t>
+    <t>Galway United</t>
   </si>
   <si>
     <t>San Luis</t>
-  </si>
-  <si>
-    <t>Galway United</t>
   </si>
   <si>
     <t>Nacional Asunción</t>
@@ -863,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD34"/>
+  <dimension ref="A1:BD38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -1047,13 +1077,13 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1068,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1143,10 +1173,10 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1217,13 +1247,13 @@
         <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1238,16 +1268,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L3">
-        <v>4.7</v>
+        <v>3.07</v>
       </c>
       <c r="M3">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="N3">
-        <v>1.71</v>
+        <v>2.13</v>
       </c>
       <c r="O3">
         <v>2.68</v>
@@ -1259,73 +1289,73 @@
         <v>1.66</v>
       </c>
       <c r="R3">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S3">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U3">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="V3">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>7.9</v>
+      </c>
+      <c r="Z3">
+        <v>1.36</v>
+      </c>
+      <c r="AA3">
+        <v>2.88</v>
+      </c>
+      <c r="AB3">
+        <v>2.32</v>
+      </c>
+      <c r="AC3">
+        <v>1.58</v>
+      </c>
+      <c r="AD3">
+        <v>3.8</v>
+      </c>
+      <c r="AE3">
+        <v>1.25</v>
+      </c>
+      <c r="AF3">
+        <v>1.8</v>
+      </c>
+      <c r="AG3">
+        <v>1.87</v>
+      </c>
+      <c r="AH3">
+        <v>7.7</v>
+      </c>
+      <c r="AI3">
         <v>1.07</v>
       </c>
-      <c r="Y3">
-        <v>7</v>
-      </c>
-      <c r="Z3">
-        <v>1.42</v>
-      </c>
-      <c r="AA3">
-        <v>2.62</v>
-      </c>
-      <c r="AB3">
-        <v>2.36</v>
-      </c>
-      <c r="AC3">
-        <v>1.55</v>
-      </c>
-      <c r="AD3">
-        <v>4.3</v>
-      </c>
-      <c r="AE3">
-        <v>1.18</v>
-      </c>
-      <c r="AF3">
-        <v>2.05</v>
-      </c>
-      <c r="AG3">
-        <v>1.76</v>
-      </c>
-      <c r="AH3">
-        <v>8.5</v>
-      </c>
-      <c r="AI3">
-        <v>1.04</v>
-      </c>
       <c r="AJ3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL3">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AM3">
         <v>1.3</v>
       </c>
       <c r="AN3">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1387,13 +1417,13 @@
         <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1408,16 +1438,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="M4">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="N4">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="O4">
         <v>2.23</v>
@@ -1429,73 +1459,73 @@
         <v>1.83</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S4">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
+        <v>1.35</v>
+      </c>
+      <c r="V4">
+        <v>7.5</v>
+      </c>
+      <c r="W4">
+        <v>1.07</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>8.5</v>
+      </c>
+      <c r="Z4">
         <v>1.33</v>
       </c>
-      <c r="V4">
-        <v>7.8</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>8.1</v>
-      </c>
-      <c r="Z4">
-        <v>1.32</v>
-      </c>
       <c r="AA4">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AD4">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="AE4">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH4">
-        <v>7.4</v>
+        <v>6.95</v>
       </c>
       <c r="AI4">
         <v>1.07</v>
       </c>
       <c r="AJ4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK4" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL4">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AM4">
         <v>1.31</v>
       </c>
       <c r="AN4">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1557,13 +1587,13 @@
         <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1578,16 +1608,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L5">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M5">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="N5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O5">
         <v>1.16</v>
@@ -1599,22 +1629,22 @@
         <v>5.3</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="U5">
         <v>1.5</v>
       </c>
       <c r="V5">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.02</v>
@@ -1623,49 +1653,49 @@
         <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA5">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AB5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC5">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AD5">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE5">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AF5">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AG5">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AH5">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AI5">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AJ5" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK5" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL5">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AM5">
         <v>1.1</v>
       </c>
       <c r="AN5">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1724,16 +1754,16 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1748,94 +1778,94 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1877,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD6" s="3">
         <v>45807.5</v>
@@ -1897,13 +1927,13 @@
         <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1918,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1993,10 +2023,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK7" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2064,16 +2094,16 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2088,94 +2118,94 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L8">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC8">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK8" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL8">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2217,10 +2247,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="BC8">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="BD8" s="3">
         <v>45807.5</v>
@@ -2237,13 +2267,13 @@
         <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F9" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2258,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L9">
         <v>1.8</v>
@@ -2273,40 +2303,40 @@
         <v>1.57</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q9">
         <v>2.63</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB9">
         <v>1.9</v>
@@ -2315,37 +2345,37 @@
         <v>1.9</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2407,13 +2437,13 @@
         <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2428,94 +2458,94 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L10">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="M10">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>4.14</v>
+        <v>2.9</v>
       </c>
       <c r="O10">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="P10">
-        <v>13.75</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="T10">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="U10">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="V10">
-        <v>6.45</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Z10">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AA10">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="AB10">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="AD10">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AE10">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH10">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AI10">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK10" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AM10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN10">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2557,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="BC10">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="BD10" s="3">
         <v>45807.54166666666</v>
@@ -2571,19 +2601,19 @@
         <v>45807</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2598,127 +2628,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L11">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="M11">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="N11">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="O11">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="P11">
-        <v>8.5</v>
+        <v>13.75</v>
       </c>
       <c r="Q11">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S11">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="U11">
+        <v>1.41</v>
+      </c>
+      <c r="V11">
+        <v>6.55</v>
+      </c>
+      <c r="W11">
+        <v>1.05</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>8.9</v>
+      </c>
+      <c r="Z11">
+        <v>1.22</v>
+      </c>
+      <c r="AA11">
+        <v>3.64</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
+        <v>2.02</v>
+      </c>
+      <c r="AD11">
+        <v>2.78</v>
+      </c>
+      <c r="AE11">
         <v>1.36</v>
       </c>
-      <c r="V11">
-        <v>7</v>
-      </c>
-      <c r="W11">
-        <v>1.06</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>10</v>
-      </c>
-      <c r="Z11">
-        <v>1.29</v>
-      </c>
-      <c r="AA11">
-        <v>3.25</v>
-      </c>
-      <c r="AB11">
-        <v>2</v>
-      </c>
-      <c r="AC11">
-        <v>1.72</v>
-      </c>
-      <c r="AD11">
-        <v>3.8</v>
-      </c>
-      <c r="AE11">
-        <v>1.22</v>
-      </c>
       <c r="AF11">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>1.89</v>
+        <v>2.13</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="AI11">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AJ11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL11">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AM11">
         <v>1.28</v>
       </c>
       <c r="AN11">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2727,13 +2757,13 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="BC11">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="BD11" s="3">
-        <v>45807.58333333334</v>
+        <v>45807.54166666666</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -2747,13 +2777,13 @@
         <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2768,127 +2798,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L12">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="M12">
-        <v>5.29</v>
+        <v>4.85</v>
       </c>
       <c r="N12">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="O12">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="P12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q12">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
         <v>1.22</v>
       </c>
       <c r="S12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T12">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="U12">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="V12">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Z12">
         <v>1.11</v>
       </c>
       <c r="AA12">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AB12">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD12">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AE12">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AH12">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AI12">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AJ12" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK12" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL12">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AM12">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AN12">
-        <v>4.45</v>
+        <v>2.6</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2897,10 +2927,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="BC12">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="BD12" s="3">
         <v>45807.58333333334</v>
@@ -2917,13 +2947,13 @@
         <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2938,127 +2968,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L13">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="M13">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="N13">
-        <v>2.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>16</v>
       </c>
       <c r="Q13">
-        <v>2.04</v>
+        <v>4.75</v>
       </c>
       <c r="R13">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="T13">
-        <v>2.93</v>
+        <v>2.11</v>
       </c>
       <c r="U13">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="V13">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="W13">
+        <v>1.2</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>16.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.11</v>
+      </c>
+      <c r="AA13">
+        <v>5.5</v>
+      </c>
+      <c r="AB13">
+        <v>1.37</v>
+      </c>
+      <c r="AC13">
+        <v>2.85</v>
+      </c>
+      <c r="AD13">
+        <v>1.94</v>
+      </c>
+      <c r="AE13">
+        <v>1.76</v>
+      </c>
+      <c r="AF13">
+        <v>2</v>
+      </c>
+      <c r="AG13">
+        <v>1.78</v>
+      </c>
+      <c r="AH13">
+        <v>3.2</v>
+      </c>
+      <c r="AI13">
+        <v>1.32</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL13">
         <v>1.08</v>
       </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>9</v>
-      </c>
-      <c r="Z13">
-        <v>1.27</v>
-      </c>
-      <c r="AA13">
-        <v>3.3</v>
-      </c>
-      <c r="AB13">
-        <v>1.98</v>
-      </c>
-      <c r="AC13">
-        <v>1.79</v>
-      </c>
-      <c r="AD13">
-        <v>3.22</v>
-      </c>
-      <c r="AE13">
-        <v>1.29</v>
-      </c>
-      <c r="AF13">
-        <v>1.73</v>
-      </c>
-      <c r="AG13">
-        <v>2</v>
-      </c>
-      <c r="AH13">
-        <v>6.05</v>
-      </c>
-      <c r="AI13">
-        <v>1.09</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL13">
-        <v>1.44</v>
-      </c>
       <c r="AM13">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AN13">
-        <v>1.53</v>
+        <v>4.45</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3067,10 +3097,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="BC13">
-        <v>2.04</v>
+        <v>4.75</v>
       </c>
       <c r="BD13" s="3">
         <v>45807.58333333334</v>
@@ -3081,19 +3111,19 @@
         <v>45807</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3108,127 +3138,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AJ14" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK14" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW14">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AY14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3237,13 +3267,13 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BC14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD14" s="3">
-        <v>45807.625</v>
+        <v>45807.58333333334</v>
       </c>
     </row>
     <row r="15" spans="1:56">
@@ -3251,19 +3281,19 @@
         <v>45807</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F15" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3278,127 +3308,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L15">
-        <v>1.81</v>
+        <v>2.33</v>
       </c>
       <c r="M15">
-        <v>3.8</v>
+        <v>3.23</v>
       </c>
       <c r="N15">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="O15">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="P15">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q15">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S15">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="T15">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V15">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA15">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AD15">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AE15">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AH15">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK15" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL15">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AM15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN15">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AQ15">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AR15">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AS15">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AT15">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="AU15">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AV15">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AW15">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AX15">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AY15">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3407,13 +3437,13 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="BC15">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="BD15" s="3">
-        <v>45807.64583333334</v>
+        <v>45807.58333333334</v>
       </c>
     </row>
     <row r="16" spans="1:56">
@@ -3421,19 +3451,19 @@
         <v>45807</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3448,127 +3478,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L16">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="M16">
-        <v>3.06</v>
+        <v>3.35</v>
       </c>
       <c r="N16">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="O16">
+        <v>2.02</v>
+      </c>
+      <c r="P16">
+        <v>8.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.04</v>
+      </c>
+      <c r="R16">
+        <v>1.38</v>
+      </c>
+      <c r="S16">
+        <v>2.81</v>
+      </c>
+      <c r="T16">
+        <v>2.77</v>
+      </c>
+      <c r="U16">
+        <v>1.39</v>
+      </c>
+      <c r="V16">
+        <v>7</v>
+      </c>
+      <c r="W16">
+        <v>1.05</v>
+      </c>
+      <c r="X16">
+        <v>1.06</v>
+      </c>
+      <c r="Y16">
+        <v>9.5</v>
+      </c>
+      <c r="Z16">
+        <v>1.27</v>
+      </c>
+      <c r="AA16">
+        <v>3.4</v>
+      </c>
+      <c r="AB16">
+        <v>1.92</v>
+      </c>
+      <c r="AC16">
+        <v>1.78</v>
+      </c>
+      <c r="AD16">
+        <v>3.22</v>
+      </c>
+      <c r="AE16">
+        <v>1.29</v>
+      </c>
+      <c r="AF16">
+        <v>1.73</v>
+      </c>
+      <c r="AG16">
         <v>2</v>
       </c>
-      <c r="P16">
-        <v>8</v>
-      </c>
-      <c r="Q16">
-        <v>2</v>
-      </c>
-      <c r="R16">
-        <v>1.41</v>
-      </c>
-      <c r="S16">
-        <v>2.6</v>
-      </c>
-      <c r="T16">
-        <v>3.04</v>
-      </c>
-      <c r="U16">
-        <v>1.35</v>
-      </c>
-      <c r="V16">
-        <v>6.8</v>
-      </c>
-      <c r="W16">
-        <v>1.01</v>
-      </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16">
-        <v>7.75</v>
-      </c>
-      <c r="Z16">
-        <v>1.32</v>
-      </c>
-      <c r="AA16">
-        <v>2.9</v>
-      </c>
-      <c r="AB16">
-        <v>2.05</v>
-      </c>
-      <c r="AC16">
-        <v>1.65</v>
-      </c>
-      <c r="AD16">
-        <v>3.85</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
-      <c r="AF16">
-        <v>1.85</v>
-      </c>
-      <c r="AG16">
-        <v>1.85</v>
-      </c>
       <c r="AH16">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AI16">
         <v>1.06</v>
       </c>
       <c r="AJ16" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK16" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL16">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AM16">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN16">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AR16">
         <v>1.7</v>
       </c>
       <c r="AS16">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AT16">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU16">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="AV16">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="AW16">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AX16">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AY16">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3577,13 +3607,13 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BC16">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BD16" s="3">
-        <v>45807.65625</v>
+        <v>45807.58333333334</v>
       </c>
     </row>
     <row r="17" spans="1:56">
@@ -3591,19 +3621,19 @@
         <v>45807</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3618,127 +3648,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L17">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="M17">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N17">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
+        <v>1.98</v>
+      </c>
+      <c r="P17">
+        <v>12</v>
+      </c>
+      <c r="Q17">
+        <v>1.9</v>
+      </c>
+      <c r="R17">
+        <v>1.29</v>
+      </c>
+      <c r="S17">
+        <v>3.25</v>
+      </c>
+      <c r="T17">
+        <v>2.3</v>
+      </c>
+      <c r="U17">
+        <v>1.53</v>
+      </c>
+      <c r="V17">
+        <v>5.25</v>
+      </c>
+      <c r="W17">
+        <v>1.13</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>10</v>
+      </c>
+      <c r="Z17">
+        <v>1.2</v>
+      </c>
+      <c r="AA17">
+        <v>4.33</v>
+      </c>
+      <c r="AB17">
         <v>1.62</v>
       </c>
-      <c r="P17">
-        <v>8</v>
-      </c>
-      <c r="Q17">
-        <v>2.63</v>
-      </c>
-      <c r="R17">
-        <v>1.44</v>
-      </c>
-      <c r="S17">
-        <v>2.62</v>
-      </c>
-      <c r="T17">
-        <v>3</v>
-      </c>
-      <c r="U17">
-        <v>1.33</v>
-      </c>
-      <c r="V17">
-        <v>7.5</v>
-      </c>
-      <c r="W17">
-        <v>1.06</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>7</v>
-      </c>
-      <c r="Z17">
-        <v>1.36</v>
-      </c>
-      <c r="AA17">
-        <v>2.9</v>
-      </c>
-      <c r="AB17">
-        <v>2.05</v>
-      </c>
       <c r="AC17">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AD17">
-        <v>3.89</v>
+        <v>2.55</v>
       </c>
       <c r="AE17">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AG17">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AH17">
-        <v>7.5</v>
+        <v>4.33</v>
       </c>
       <c r="AI17">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AJ17" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK17" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL17">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="AM17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN17">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3747,13 +3777,13 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="BC17">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="BD17" s="3">
-        <v>45807.65625</v>
+        <v>45807.58333333334</v>
       </c>
     </row>
     <row r="18" spans="1:56">
@@ -3761,19 +3791,19 @@
         <v>45807</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3788,127 +3818,127 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L18">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC18">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH18">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK18" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL18">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ18">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AR18">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT18">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AU18">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV18">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AW18">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AX18">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY18">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3917,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BC18">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BD18" s="3">
-        <v>45807.65625</v>
+        <v>45807.625</v>
       </c>
     </row>
     <row r="19" spans="1:56">
@@ -3931,19 +3961,19 @@
         <v>45807</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
         <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3958,127 +3988,127 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L19">
         <v>1.81</v>
       </c>
       <c r="M19">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N19">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O19">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="R19">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S19">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T19">
-        <v>2.76</v>
+        <v>2.37</v>
       </c>
       <c r="U19">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z19">
+        <v>1.2</v>
+      </c>
+      <c r="AA19">
+        <v>4.33</v>
+      </c>
+      <c r="AB19">
+        <v>1.65</v>
+      </c>
+      <c r="AC19">
+        <v>2.05</v>
+      </c>
+      <c r="AD19">
+        <v>2.6</v>
+      </c>
+      <c r="AE19">
+        <v>1.48</v>
+      </c>
+      <c r="AF19">
+        <v>1.6</v>
+      </c>
+      <c r="AG19">
+        <v>2.2</v>
+      </c>
+      <c r="AH19">
+        <v>4.75</v>
+      </c>
+      <c r="AI19">
+        <v>1.18</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL19">
         <v>1.27</v>
       </c>
-      <c r="AA19">
-        <v>3.5</v>
-      </c>
-      <c r="AB19">
+      <c r="AM19">
+        <v>1.26</v>
+      </c>
+      <c r="AN19">
         <v>1.85</v>
-      </c>
-      <c r="AC19">
-        <v>1.83</v>
-      </c>
-      <c r="AD19">
-        <v>3.1</v>
-      </c>
-      <c r="AE19">
-        <v>1.32</v>
-      </c>
-      <c r="AF19">
-        <v>1.7</v>
-      </c>
-      <c r="AG19">
-        <v>2</v>
-      </c>
-      <c r="AH19">
-        <v>6.35</v>
-      </c>
-      <c r="AI19">
-        <v>1.09</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL19">
-        <v>1.25</v>
-      </c>
-      <c r="AM19">
-        <v>0</v>
-      </c>
-      <c r="AN19">
-        <v>1.9</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4087,13 +4117,13 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="BC19">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="BD19" s="3">
-        <v>45807.65625</v>
+        <v>45807.64583333334</v>
       </c>
     </row>
     <row r="20" spans="1:56">
@@ -4104,16 +4134,16 @@
         <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4128,127 +4158,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L20">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="M20">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="N20">
-        <v>1.54</v>
+        <v>3.83</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="P20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S20">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T20">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="Z20">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA20">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB20">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD20">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AE20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH20">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AI20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ20" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK20" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL20">
         <v>1.25</v>
       </c>
       <c r="AM20">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>1.13</v>
+        <v>1.85</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4257,10 +4287,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="BC20">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="BD20" s="3">
         <v>45807.65625</v>
@@ -4274,16 +4304,16 @@
         <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4298,127 +4328,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L21">
-        <v>1.79</v>
+        <v>2.47</v>
       </c>
       <c r="M21">
-        <v>3.45</v>
+        <v>3.02</v>
       </c>
       <c r="N21">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="P21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R21">
+        <v>1.5</v>
+      </c>
+      <c r="S21">
+        <v>2.4</v>
+      </c>
+      <c r="T21">
+        <v>3.25</v>
+      </c>
+      <c r="U21">
+        <v>1.29</v>
+      </c>
+      <c r="V21">
+        <v>7.5</v>
+      </c>
+      <c r="W21">
+        <v>1.01</v>
+      </c>
+      <c r="X21">
+        <v>1.09</v>
+      </c>
+      <c r="Y21">
+        <v>7</v>
+      </c>
+      <c r="Z21">
+        <v>1.45</v>
+      </c>
+      <c r="AA21">
+        <v>2.7</v>
+      </c>
+      <c r="AB21">
+        <v>2.25</v>
+      </c>
+      <c r="AC21">
+        <v>1.53</v>
+      </c>
+      <c r="AD21">
+        <v>4.33</v>
+      </c>
+      <c r="AE21">
+        <v>1.18</v>
+      </c>
+      <c r="AF21">
+        <v>2</v>
+      </c>
+      <c r="AG21">
+        <v>1.75</v>
+      </c>
+      <c r="AH21">
+        <v>7.2</v>
+      </c>
+      <c r="AI21">
+        <v>1.06</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL21">
+        <v>1.4</v>
+      </c>
+      <c r="AM21">
         <v>1.3</v>
       </c>
-      <c r="S21">
-        <v>3.24</v>
-      </c>
-      <c r="T21">
-        <v>2.4</v>
-      </c>
-      <c r="U21">
-        <v>1.47</v>
-      </c>
-      <c r="V21">
-        <v>5.5</v>
-      </c>
-      <c r="W21">
-        <v>1.12</v>
-      </c>
-      <c r="X21">
-        <v>1.03</v>
-      </c>
-      <c r="Y21">
-        <v>10</v>
-      </c>
-      <c r="Z21">
-        <v>1.22</v>
-      </c>
-      <c r="AA21">
-        <v>4</v>
-      </c>
-      <c r="AB21">
-        <v>1.7</v>
-      </c>
-      <c r="AC21">
-        <v>1.95</v>
-      </c>
-      <c r="AD21">
-        <v>2.74</v>
-      </c>
-      <c r="AE21">
-        <v>1.4</v>
-      </c>
-      <c r="AF21">
-        <v>1.7</v>
-      </c>
-      <c r="AG21">
-        <v>2</v>
-      </c>
-      <c r="AH21">
-        <v>4.75</v>
-      </c>
-      <c r="AI21">
-        <v>1.15</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK21" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL21">
-        <v>1.25</v>
-      </c>
-      <c r="AM21">
-        <v>1.2</v>
-      </c>
       <c r="AN21">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4427,10 +4457,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="BC21">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" s="3">
         <v>45807.65625</v>
@@ -4444,16 +4474,16 @@
         <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4468,127 +4498,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L22">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="M22">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="O22">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="P22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="U22">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V22">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W22">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Z22">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AA22">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AB22">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AD22">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AG22">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH22">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AI22">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AJ22" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK22" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL22">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AM22">
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ22">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AR22">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AS22">
+        <v>2.25</v>
+      </c>
+      <c r="AT22">
+        <v>2.92</v>
+      </c>
+      <c r="AU22">
+        <v>3.58</v>
+      </c>
+      <c r="AV22">
         <v>2.4</v>
       </c>
-      <c r="AT22">
-        <v>3.07</v>
-      </c>
-      <c r="AU22">
-        <v>2.95</v>
-      </c>
-      <c r="AV22">
-        <v>2.23</v>
-      </c>
       <c r="AW22">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AX22">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AY22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4597,10 +4627,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BC22">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BD22" s="3">
         <v>45807.65625</v>
@@ -4614,16 +4644,16 @@
         <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4638,127 +4668,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L23">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="M23">
-        <v>3.47</v>
+        <v>3.11</v>
       </c>
       <c r="N23">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="O23">
         <v>2.75</v>
       </c>
       <c r="P23">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="R23">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="S23">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="V23">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>8.1</v>
       </c>
       <c r="Z23">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AA23">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AB23">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AC23">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AD23">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AE23">
+        <v>1.21</v>
+      </c>
+      <c r="AF23">
+        <v>2</v>
+      </c>
+      <c r="AG23">
+        <v>1.67</v>
+      </c>
+      <c r="AH23">
+        <v>6.7</v>
+      </c>
+      <c r="AI23">
+        <v>1.06</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL23">
         <v>1.33</v>
       </c>
-      <c r="AF23">
-        <v>1.76</v>
-      </c>
-      <c r="AG23">
-        <v>2</v>
-      </c>
-      <c r="AH23">
-        <v>5.45</v>
-      </c>
-      <c r="AI23">
-        <v>1.11</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL23">
-        <v>1.93</v>
-      </c>
       <c r="AM23">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AN23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ23">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AR23">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AS23">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="AT23">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="AU23">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AV23">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AW23">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AX23">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AY23">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4770,7 +4800,7 @@
         <v>2.75</v>
       </c>
       <c r="BC23">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="BD23" s="3">
         <v>45807.65625</v>
@@ -4784,16 +4814,16 @@
         <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -4808,127 +4838,127 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L24">
-        <v>1.92</v>
+        <v>5.7</v>
       </c>
       <c r="M24">
+        <v>4.1</v>
+      </c>
+      <c r="N24">
+        <v>1.47</v>
+      </c>
+      <c r="O24">
         <v>3.25</v>
-      </c>
-      <c r="N24">
-        <v>3.6</v>
-      </c>
-      <c r="O24">
-        <v>1.5</v>
       </c>
       <c r="P24">
         <v>9</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="R24">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S24">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V24">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AA24">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB24">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC24">
         <v>1.91</v>
       </c>
       <c r="AD24">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH24">
-        <v>5.09</v>
+        <v>4.7</v>
       </c>
       <c r="AI24">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK24" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL24">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AM24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN24">
-        <v>1.95</v>
+        <v>1.09</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4937,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="BC24">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="BD24" s="3">
         <v>45807.65625</v>
@@ -4951,19 +4981,19 @@
         <v>45807</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
         <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -4978,127 +5008,127 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L25">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="M25">
-        <v>3.05</v>
+        <v>3.47</v>
       </c>
       <c r="N25">
-        <v>2.71</v>
+        <v>3.88</v>
       </c>
       <c r="O25">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="P25">
+        <v>8</v>
+      </c>
+      <c r="Q25">
+        <v>2.63</v>
+      </c>
+      <c r="R25">
+        <v>1.39</v>
+      </c>
+      <c r="S25">
+        <v>2.6</v>
+      </c>
+      <c r="T25">
+        <v>2.8</v>
+      </c>
+      <c r="U25">
+        <v>1.34</v>
+      </c>
+      <c r="V25">
         <v>7</v>
       </c>
-      <c r="Q25">
-        <v>2.3</v>
-      </c>
-      <c r="R25">
-        <v>1.49</v>
-      </c>
-      <c r="S25">
-        <v>2.44</v>
-      </c>
-      <c r="T25">
-        <v>3.3</v>
-      </c>
-      <c r="U25">
-        <v>1.29</v>
-      </c>
-      <c r="V25">
-        <v>8.5</v>
-      </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>6.8</v>
+        <v>7.75</v>
       </c>
       <c r="Z25">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AA25">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="AB25">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AD25">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AF25">
+        <v>1.83</v>
+      </c>
+      <c r="AG25">
         <v>1.95</v>
       </c>
-      <c r="AG25">
-        <v>1.7</v>
-      </c>
       <c r="AH25">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AI25">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AJ25" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK25" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AM25">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AN25">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU25">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AV25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW25">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX25">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5107,13 +5137,13 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="BC25">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="BD25" s="3">
-        <v>45807.66666666666</v>
+        <v>45807.65625</v>
       </c>
     </row>
     <row r="26" spans="1:56">
@@ -5121,19 +5151,19 @@
         <v>45807</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F26" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -5148,85 +5178,85 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L26">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="M26">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="N26">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P26">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="R26">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S26">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="T26">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U26">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="V26">
-        <v>7.75</v>
+        <v>5.5</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z26">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AA26">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AB26">
+        <v>1.7</v>
+      </c>
+      <c r="AC26">
+        <v>1.95</v>
+      </c>
+      <c r="AD26">
+        <v>2.88</v>
+      </c>
+      <c r="AE26">
+        <v>1.38</v>
+      </c>
+      <c r="AF26">
+        <v>1.7</v>
+      </c>
+      <c r="AG26">
         <v>2</v>
       </c>
-      <c r="AC26">
-        <v>1.67</v>
-      </c>
-      <c r="AD26">
-        <v>3.72</v>
-      </c>
-      <c r="AE26">
-        <v>1.21</v>
-      </c>
-      <c r="AF26">
-        <v>2.15</v>
-      </c>
-      <c r="AG26">
-        <v>1.67</v>
-      </c>
       <c r="AH26">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI26">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ26" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK26" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL26">
         <v>1.25</v>
@@ -5235,40 +5265,40 @@
         <v>1.2</v>
       </c>
       <c r="AN26">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AR26">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AS26">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AT26">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AU26">
-        <v>3.05</v>
+        <v>3.88</v>
       </c>
       <c r="AV26">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="AW26">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AX26">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AY26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5277,13 +5307,13 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BC26">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="BD26" s="3">
-        <v>45807.66666666666</v>
+        <v>45807.65625</v>
       </c>
     </row>
     <row r="27" spans="1:56">
@@ -5291,19 +5321,19 @@
         <v>45807</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F27" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -5318,142 +5348,142 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L27">
-        <v>3.5</v>
+        <v>1.74</v>
       </c>
       <c r="M27">
-        <v>2.9</v>
+        <v>3.64</v>
       </c>
       <c r="N27">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="O27">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="P27">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S27">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="U27">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V27">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="W27">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>9.75</v>
       </c>
       <c r="Z27">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="AA27">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="AB27">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AC27">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AD27">
-        <v>4.6</v>
+        <v>2.74</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="AF27">
+        <v>1.68</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27">
+        <v>5.25</v>
+      </c>
+      <c r="AI27">
+        <v>1.06</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL27">
+        <v>1.22</v>
+      </c>
+      <c r="AM27">
+        <v>1.22</v>
+      </c>
+      <c r="AN27">
         <v>2.05</v>
-      </c>
-      <c r="AG27">
-        <v>1.7</v>
-      </c>
-      <c r="AH27">
-        <v>10</v>
-      </c>
-      <c r="AI27">
-        <v>1.05</v>
-      </c>
-      <c r="AJ27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AK27" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL27">
-        <v>1.4</v>
-      </c>
-      <c r="AM27">
-        <v>1.36</v>
-      </c>
-      <c r="AN27">
-        <v>1.29</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
+        <v>1.19</v>
+      </c>
+      <c r="AQ27">
+        <v>1.38</v>
+      </c>
+      <c r="AR27">
+        <v>1.69</v>
+      </c>
+      <c r="AS27">
+        <v>2.12</v>
+      </c>
+      <c r="AT27">
+        <v>2.7</v>
+      </c>
+      <c r="AU27">
+        <v>3.6</v>
+      </c>
+      <c r="AV27">
+        <v>2.62</v>
+      </c>
+      <c r="AW27">
+        <v>2</v>
+      </c>
+      <c r="AX27">
+        <v>1.58</v>
+      </c>
+      <c r="AY27">
+        <v>1.4</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
         <v>1.5</v>
       </c>
-      <c r="AQ27">
-        <v>1.85</v>
-      </c>
-      <c r="AR27">
-        <v>2.35</v>
-      </c>
-      <c r="AS27">
-        <v>3.05</v>
-      </c>
-      <c r="AT27">
-        <v>4.1</v>
-      </c>
-      <c r="AU27">
-        <v>2.35</v>
-      </c>
-      <c r="AV27">
-        <v>1.81</v>
-      </c>
-      <c r="AW27">
-        <v>1.5</v>
-      </c>
-      <c r="AX27">
-        <v>1.3</v>
-      </c>
-      <c r="AY27">
-        <v>1.17</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>2.5</v>
-      </c>
       <c r="BC27">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="BD27" s="3">
-        <v>45807.70833333334</v>
+        <v>45807.65625</v>
       </c>
     </row>
     <row r="28" spans="1:56">
@@ -5461,19 +5491,19 @@
         <v>45807</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -5488,127 +5518,127 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ28" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK28" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO28">
         <v>-1</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5617,13 +5647,13 @@
         <v>0</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BD28" s="3">
-        <v>45807.75</v>
+        <v>45807.65625</v>
       </c>
     </row>
     <row r="29" spans="1:56">
@@ -5631,19 +5661,19 @@
         <v>45807</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -5658,127 +5688,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L29">
-        <v>2.42</v>
+        <v>1.5</v>
       </c>
       <c r="M29">
-        <v>2.94</v>
+        <v>3.64</v>
       </c>
       <c r="N29">
-        <v>2.73</v>
+        <v>5.6</v>
       </c>
       <c r="O29">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="P29">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="R29">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="S29">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="U29">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="V29">
-        <v>11.5</v>
+        <v>7.75</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>5.5</v>
+        <v>9.65</v>
       </c>
       <c r="Z29">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AA29">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB29">
-        <v>2.37</v>
+        <v>1.94</v>
       </c>
       <c r="AC29">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AD29">
-        <v>6.2</v>
+        <v>3.54</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AF29">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AG29">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AH29">
-        <v>11</v>
+        <v>6.85</v>
       </c>
       <c r="AI29">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK29" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL29">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="AM29">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="AN29">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ29">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AR29">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AS29">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AT29">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AU29">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AV29">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AW29">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AX29">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AY29">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5787,13 +5817,13 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="BC29">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="BD29" s="3">
-        <v>45807.79166666666</v>
+        <v>45807.66666666666</v>
       </c>
     </row>
     <row r="30" spans="1:56">
@@ -5801,19 +5831,19 @@
         <v>45807</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
         <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -5828,94 +5858,94 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AJ30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK30" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO30">
         <v>-1</v>
@@ -5957,13 +5987,13 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD30" s="3">
-        <v>45807.83333333334</v>
+        <v>45807.66666666666</v>
       </c>
     </row>
     <row r="31" spans="1:56">
@@ -5971,19 +6001,19 @@
         <v>45807</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F31" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -5998,127 +6028,127 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L31">
-        <v>1.96</v>
+        <v>3.5</v>
       </c>
       <c r="M31">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="N31">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="O31">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="P31">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Q31">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="R31">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="Z31">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="AA31">
-        <v>2.88</v>
+        <v>2.37</v>
       </c>
       <c r="AB31">
+        <v>2.5</v>
+      </c>
+      <c r="AC31">
+        <v>1.49</v>
+      </c>
+      <c r="AD31">
+        <v>4.7</v>
+      </c>
+      <c r="AE31">
+        <v>1.15</v>
+      </c>
+      <c r="AF31">
         <v>2.1</v>
       </c>
-      <c r="AC31">
-        <v>1.65</v>
-      </c>
-      <c r="AD31">
-        <v>3.84</v>
-      </c>
-      <c r="AE31">
-        <v>1.22</v>
-      </c>
-      <c r="AF31">
-        <v>1.91</v>
-      </c>
       <c r="AG31">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI31">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK31" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL31">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AN31">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU31">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AY31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6127,13 +6157,13 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BC31">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="BD31" s="3">
-        <v>45807.875</v>
+        <v>45807.70833333334</v>
       </c>
     </row>
     <row r="32" spans="1:56">
@@ -6141,19 +6171,19 @@
         <v>45807</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F32" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6168,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -6243,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK32" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6303,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="BD32" s="3">
-        <v>45807.89583333334</v>
+        <v>45807.75</v>
       </c>
     </row>
     <row r="33" spans="1:56">
@@ -6311,19 +6341,19 @@
         <v>45807</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F33" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6338,127 +6368,127 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L33">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="M33">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="N33">
-        <v>3.07</v>
+        <v>2.73</v>
       </c>
       <c r="O33">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="P33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="S33">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="T33">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="W33">
         <v>1.02</v>
       </c>
       <c r="X33">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>4.78</v>
+        <v>5.5</v>
       </c>
       <c r="Z33">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="AA33">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="AB33">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="AC33">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AD33">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AG33">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AH33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI33">
         <v>1.01</v>
       </c>
       <c r="AJ33" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK33" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL33">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AM33">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AN33">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AO33">
         <v>-1</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AQ33">
-        <v>1.84</v>
+        <v>1.32</v>
       </c>
       <c r="AR33">
-        <v>2.33</v>
+        <v>1.6</v>
       </c>
       <c r="AS33">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="AT33">
-        <v>4.1</v>
+        <v>2.6</v>
       </c>
       <c r="AU33">
-        <v>2.38</v>
+        <v>3.7</v>
       </c>
       <c r="AV33">
-        <v>1.84</v>
+        <v>2.7</v>
       </c>
       <c r="AW33">
-        <v>1.5</v>
+        <v>2.08</v>
       </c>
       <c r="AX33">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AY33">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -6467,13 +6497,13 @@
         <v>0</v>
       </c>
       <c r="BB33">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="BC33">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="BD33" s="3">
-        <v>45807.91666666666</v>
+        <v>45807.79166666666</v>
       </c>
     </row>
     <row r="34" spans="1:56">
@@ -6481,19 +6511,19 @@
         <v>45807</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F34" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -6508,43 +6538,43 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L34">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M34">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X34">
         <v>0</v>
@@ -6559,22 +6589,22 @@
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH34">
         <v>0</v>
@@ -6583,10 +6613,10 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AK34" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6637,12 +6667,692 @@
         <v>0</v>
       </c>
       <c r="BB34">
+        <v>0</v>
+      </c>
+      <c r="BC34">
+        <v>0</v>
+      </c>
+      <c r="BD34" s="3">
+        <v>45807.83333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:56">
+      <c r="A35" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" t="s">
+        <v>166</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35">
+        <v>1.96</v>
+      </c>
+      <c r="M35">
+        <v>3.16</v>
+      </c>
+      <c r="N35">
+        <v>3.4</v>
+      </c>
+      <c r="O35">
+        <v>1.67</v>
+      </c>
+      <c r="P35">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>2.63</v>
+      </c>
+      <c r="R35">
+        <v>1.4</v>
+      </c>
+      <c r="S35">
+        <v>2.49</v>
+      </c>
+      <c r="T35">
+        <v>3</v>
+      </c>
+      <c r="U35">
+        <v>1.3</v>
+      </c>
+      <c r="V35">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W35">
+        <v>1.03</v>
+      </c>
+      <c r="X35">
+        <v>1.08</v>
+      </c>
+      <c r="Y35">
+        <v>6.2</v>
+      </c>
+      <c r="Z35">
+        <v>1.36</v>
+      </c>
+      <c r="AA35">
+        <v>2.9</v>
+      </c>
+      <c r="AB35">
+        <v>2.05</v>
+      </c>
+      <c r="AC35">
+        <v>1.61</v>
+      </c>
+      <c r="AD35">
+        <v>3.8</v>
+      </c>
+      <c r="AE35">
+        <v>1.22</v>
+      </c>
+      <c r="AF35">
+        <v>1.93</v>
+      </c>
+      <c r="AG35">
+        <v>1.8</v>
+      </c>
+      <c r="AH35">
+        <v>8</v>
+      </c>
+      <c r="AI35">
+        <v>1.01</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL35">
+        <v>1.25</v>
+      </c>
+      <c r="AM35">
+        <v>1.28</v>
+      </c>
+      <c r="AN35">
+        <v>1.61</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>0</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35">
+        <v>0</v>
+      </c>
+      <c r="AV35">
+        <v>0</v>
+      </c>
+      <c r="AW35">
+        <v>0</v>
+      </c>
+      <c r="AX35">
+        <v>0</v>
+      </c>
+      <c r="AY35">
+        <v>0</v>
+      </c>
+      <c r="AZ35">
+        <v>0</v>
+      </c>
+      <c r="BA35">
+        <v>0</v>
+      </c>
+      <c r="BB35">
+        <v>1.67</v>
+      </c>
+      <c r="BC35">
+        <v>2.63</v>
+      </c>
+      <c r="BD35" s="3">
+        <v>45807.875</v>
+      </c>
+    </row>
+    <row r="36" spans="1:56">
+      <c r="A36" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" t="s">
+        <v>130</v>
+      </c>
+      <c r="F36" t="s">
+        <v>167</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>170</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>0</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36" s="3">
+        <v>45807.89583333334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:56">
+      <c r="A37" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>170</v>
+      </c>
+      <c r="L37">
+        <v>2.24</v>
+      </c>
+      <c r="M37">
+        <v>2.88</v>
+      </c>
+      <c r="N37">
+        <v>3.07</v>
+      </c>
+      <c r="O37">
+        <v>1.83</v>
+      </c>
+      <c r="P37">
+        <v>5</v>
+      </c>
+      <c r="Q37">
+        <v>2.63</v>
+      </c>
+      <c r="R37">
+        <v>1.8</v>
+      </c>
+      <c r="S37">
+        <v>1.91</v>
+      </c>
+      <c r="T37">
+        <v>4.4</v>
+      </c>
+      <c r="U37">
+        <v>1.15</v>
+      </c>
+      <c r="V37">
+        <v>14</v>
+      </c>
+      <c r="W37">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>1.14</v>
+      </c>
+      <c r="Y37">
+        <v>5</v>
+      </c>
+      <c r="Z37">
+        <v>1.74</v>
+      </c>
+      <c r="AA37">
+        <v>1.96</v>
+      </c>
+      <c r="AB37">
+        <v>3.5</v>
+      </c>
+      <c r="AC37">
+        <v>1.25</v>
+      </c>
+      <c r="AD37">
+        <v>6.5</v>
+      </c>
+      <c r="AE37">
+        <v>1.1</v>
+      </c>
+      <c r="AF37">
+        <v>2.5</v>
+      </c>
+      <c r="AG37">
+        <v>1.42</v>
+      </c>
+      <c r="AH37">
+        <v>15</v>
+      </c>
+      <c r="AI37">
+        <v>1.01</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL37">
+        <v>1.25</v>
+      </c>
+      <c r="AM37">
+        <v>1.39</v>
+      </c>
+      <c r="AN37">
+        <v>1.57</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>1.44</v>
+      </c>
+      <c r="AQ37">
+        <v>1.73</v>
+      </c>
+      <c r="AR37">
+        <v>2.66</v>
+      </c>
+      <c r="AS37">
+        <v>2.88</v>
+      </c>
+      <c r="AT37">
+        <v>4.4</v>
+      </c>
+      <c r="AU37">
+        <v>2.6</v>
+      </c>
+      <c r="AV37">
+        <v>2</v>
+      </c>
+      <c r="AW37">
+        <v>1.6</v>
+      </c>
+      <c r="AX37">
+        <v>1.36</v>
+      </c>
+      <c r="AY37">
+        <v>1.16</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>1.83</v>
+      </c>
+      <c r="BC37">
+        <v>2.63</v>
+      </c>
+      <c r="BD37" s="3">
+        <v>45807.91666666666</v>
+      </c>
+    </row>
+    <row r="38" spans="1:56">
+      <c r="A38" s="2">
+        <v>45807</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>170</v>
+      </c>
+      <c r="L38">
+        <v>2.7</v>
+      </c>
+      <c r="M38">
+        <v>3.55</v>
+      </c>
+      <c r="N38">
+        <v>2.18</v>
+      </c>
+      <c r="O38">
         <v>2.2</v>
       </c>
-      <c r="BC34">
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <v>1.73</v>
       </c>
-      <c r="BD34" s="3">
+      <c r="R38">
+        <v>1.25</v>
+      </c>
+      <c r="S38">
+        <v>3.75</v>
+      </c>
+      <c r="T38">
+        <v>2.2</v>
+      </c>
+      <c r="U38">
+        <v>1.62</v>
+      </c>
+      <c r="V38">
+        <v>4.5</v>
+      </c>
+      <c r="W38">
+        <v>1.17</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>1.72</v>
+      </c>
+      <c r="AC38">
+        <v>2.07</v>
+      </c>
+      <c r="AD38">
+        <v>2.2</v>
+      </c>
+      <c r="AE38">
+        <v>1.55</v>
+      </c>
+      <c r="AF38">
+        <v>1.53</v>
+      </c>
+      <c r="AG38">
+        <v>2.38</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>171</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>2.2</v>
+      </c>
+      <c r="BC38">
+        <v>1.73</v>
+      </c>
+      <c r="BD38" s="3">
         <v>45807.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-05-30.xlsx
+++ b/jogos_2025-05-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="175">
   <si>
     <t>Date</t>
   </si>
@@ -262,15 +262,15 @@
     <t>Turkey Süper Lig</t>
   </si>
   <si>
+    <t>Sweden Superettan</t>
+  </si>
+  <si>
+    <t>Norway First Division</t>
+  </si>
+  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Sweden Superettan</t>
-  </si>
-  <si>
-    <t>Norway First Division</t>
-  </si>
-  <si>
     <t>Spain Segunda División</t>
   </si>
   <si>
@@ -316,15 +316,15 @@
     <t>Tobol</t>
   </si>
   <si>
+    <t>Igman Konjic</t>
+  </si>
+  <si>
     <t>Aktobe</t>
   </si>
   <si>
     <t>GOŠK Gabela</t>
   </si>
   <si>
-    <t>Igman Konjic</t>
-  </si>
-  <si>
     <t>Bijelo Brdo</t>
   </si>
   <si>
@@ -334,57 +334,57 @@
     <t>Dinamo Brest</t>
   </si>
   <si>
+    <t>Kasımpaşa</t>
+  </si>
+  <si>
     <t>Galatasaray</t>
   </si>
   <si>
+    <t>Antalyaspor</t>
+  </si>
+  <si>
+    <t>Örebro</t>
+  </si>
+  <si>
+    <t>Skeid</t>
+  </si>
+  <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Kasımpaşa</t>
-  </si>
-  <si>
-    <t>Örebro</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
-    <t>Antalyaspor</t>
-  </si>
-  <si>
     <t>Široki Brijeg</t>
   </si>
   <si>
     <t>CD Castellón</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Sligo Rovers</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Sligo Rovers</t>
-  </si>
-  <si>
     <t>Shamrock Rovers</t>
   </si>
   <si>
@@ -427,15 +427,15 @@
     <t>Atyrau</t>
   </si>
   <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
     <t>Zrinjski</t>
   </si>
   <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
     <t>Dubrava Zagreb</t>
   </si>
   <si>
@@ -445,57 +445,57 @@
     <t>Isloch</t>
   </si>
   <si>
+    <t>Göztepe</t>
+  </si>
+  <si>
     <t>İstanbul Başakşehir</t>
   </si>
   <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>Brage</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
     <t>Tammeka</t>
   </si>
   <si>
-    <t>Göztepe</t>
-  </si>
-  <si>
-    <t>Brage</t>
-  </si>
-  <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>Sloboda Tuzla</t>
   </si>
   <si>
     <t>Real Zaragoza</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Longford Town</t>
   </si>
   <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
     <t>Galway United</t>
   </si>
   <si>
@@ -526,10 +526,19 @@
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['57']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['63', '85', '90']</t>
   </si>
 </sst>
 </file>
@@ -1086,10 +1095,10 @@
         <v>133</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1101,124 +1110,124 @@
         <v>170</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1227,10 +1236,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD2" s="3">
         <v>45807.33333333334</v>
@@ -1268,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L3">
         <v>3.07</v>
@@ -1289,106 +1298,106 @@
         <v>1.66</v>
       </c>
       <c r="R3">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S3">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T3">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z3">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA3">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AB3">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD3">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AE3">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AH3">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="AI3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AJ3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL3">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AM3">
         <v>1.3</v>
       </c>
       <c r="AN3">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AO3">
         <v>-1</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1438,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L4">
         <v>2.68</v>
@@ -1459,64 +1468,64 @@
         <v>1.83</v>
       </c>
       <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
+        <v>2.93</v>
+      </c>
+      <c r="T4">
+        <v>2.8</v>
+      </c>
+      <c r="U4">
         <v>1.4</v>
       </c>
-      <c r="S4">
-        <v>2.65</v>
-      </c>
-      <c r="T4">
-        <v>2.98</v>
-      </c>
-      <c r="U4">
-        <v>1.35</v>
-      </c>
       <c r="V4">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z4">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AA4">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="AB4">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="AC4">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AD4">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AE4">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG4">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AH4">
-        <v>6.95</v>
+        <v>5.75</v>
       </c>
       <c r="AI4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL4">
         <v>1.3</v>
@@ -1525,40 +1534,40 @@
         <v>1.31</v>
       </c>
       <c r="AN4">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1608,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L5">
         <v>1.18</v>
@@ -1632,103 +1641,103 @@
         <v>1.31</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>5.8</v>
+        <v>5.55</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AB5">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AC5">
-        <v>2.09</v>
+        <v>1.89</v>
       </c>
       <c r="AD5">
         <v>2.69</v>
       </c>
       <c r="AE5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF5">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG5">
-        <v>1.37</v>
+        <v>1.9</v>
       </c>
       <c r="AH5">
         <v>4.6</v>
       </c>
       <c r="AI5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AJ5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL5">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AM5">
         <v>1.1</v>
       </c>
       <c r="AN5">
-        <v>4.75</v>
+        <v>2.46</v>
       </c>
       <c r="AO5">
         <v>-1</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ5">
         <v>0</v>
@@ -1754,10 +1763,10 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>100</v>
@@ -1778,94 +1787,94 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L6">
-        <v>2.38</v>
+        <v>6.2</v>
       </c>
       <c r="M6">
-        <v>3.07</v>
+        <v>3.59</v>
       </c>
       <c r="N6">
-        <v>2.68</v>
+        <v>1.52</v>
       </c>
       <c r="O6">
-        <v>1.82</v>
+        <v>3.46</v>
       </c>
       <c r="P6">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Q6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="R6">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T6">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>8.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA6">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD6">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="AE6">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AF6">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AG6">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AH6">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AI6">
         <v>1.07</v>
       </c>
       <c r="AJ6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL6">
-        <v>1.28</v>
+        <v>2.67</v>
       </c>
       <c r="AM6">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AN6">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1877,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS6">
         <v>0</v>
@@ -1892,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AX6">
         <v>0</v>
@@ -1907,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.82</v>
+        <v>3.46</v>
       </c>
       <c r="BC6">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="BD6" s="3">
         <v>45807.5</v>
@@ -1924,10 +1933,10 @@
         <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>101</v>
@@ -1948,127 +1957,127 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2077,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" s="3">
         <v>45807.5</v>
@@ -2118,94 +2127,94 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2247,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BD8" s="3">
         <v>45807.5</v>
@@ -2288,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L9">
         <v>1.8</v>
@@ -2363,10 +2372,10 @@
         <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL9">
         <v>1.18</v>
@@ -2387,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -2402,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX9">
         <v>0</v>
@@ -2458,16 +2467,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L10">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N10">
-        <v>2.9</v>
+        <v>3.03</v>
       </c>
       <c r="O10">
         <v>1.85</v>
@@ -2485,28 +2494,28 @@
         <v>2.4</v>
       </c>
       <c r="T10">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="U10">
         <v>1.25</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y10">
-        <v>7.8</v>
+        <v>6.75</v>
       </c>
       <c r="Z10">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AA10">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB10">
         <v>2.06</v>
@@ -2515,28 +2524,28 @@
         <v>1.68</v>
       </c>
       <c r="AD10">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE10">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI10">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK10" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL10">
         <v>1.3</v>
@@ -2545,16 +2554,16 @@
         <v>1.25</v>
       </c>
       <c r="AN10">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -2566,10 +2575,10 @@
         <v>0</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW10">
         <v>0</v>
@@ -2628,16 +2637,16 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L11">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="M11">
         <v>3</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="O11">
         <v>1.65</v>
@@ -2652,70 +2661,70 @@
         <v>1.4</v>
       </c>
       <c r="S11">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T11">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="U11">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>6.55</v>
+        <v>9</v>
       </c>
       <c r="W11">
+        <v>1.06</v>
+      </c>
+      <c r="X11">
         <v>1.05</v>
       </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
       <c r="Y11">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AA11">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="AD11">
-        <v>2.78</v>
+        <v>3.88</v>
       </c>
       <c r="AE11">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="AH11">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="AI11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AM11">
         <v>1.28</v>
       </c>
       <c r="AN11">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AO11">
         <v>-1</v>
@@ -2798,49 +2807,49 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L12">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="M12">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="P12">
+        <v>18</v>
+      </c>
+      <c r="Q12">
+        <v>2.15</v>
+      </c>
+      <c r="R12">
+        <v>1.2</v>
+      </c>
+      <c r="S12">
+        <v>4.1</v>
+      </c>
+      <c r="T12">
+        <v>1.9</v>
+      </c>
+      <c r="U12">
+        <v>1.78</v>
+      </c>
+      <c r="V12">
+        <v>3.9</v>
+      </c>
+      <c r="W12">
+        <v>1.22</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
         <v>17</v>
-      </c>
-      <c r="Q12">
-        <v>2.9</v>
-      </c>
-      <c r="R12">
-        <v>1.22</v>
-      </c>
-      <c r="S12">
-        <v>3.9</v>
-      </c>
-      <c r="T12">
-        <v>1.98</v>
-      </c>
-      <c r="U12">
-        <v>1.73</v>
-      </c>
-      <c r="V12">
-        <v>4.1</v>
-      </c>
-      <c r="W12">
-        <v>1.2</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>11</v>
       </c>
       <c r="Z12">
         <v>1.11</v>
@@ -2849,88 +2858,88 @@
         <v>6.25</v>
       </c>
       <c r="AB12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC12">
         <v>3.1</v>
       </c>
       <c r="AD12">
+        <v>1.9</v>
+      </c>
+      <c r="AE12">
         <v>1.85</v>
       </c>
-      <c r="AE12">
-        <v>1.9</v>
-      </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AG12">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AH12">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AI12">
         <v>1.38</v>
       </c>
       <c r="AJ12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL12">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AM12">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AN12">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AQ12">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AR12">
+        <v>1.73</v>
+      </c>
+      <c r="AS12">
+        <v>2.15</v>
+      </c>
+      <c r="AT12">
+        <v>2.7</v>
+      </c>
+      <c r="AU12">
+        <v>3.4</v>
+      </c>
+      <c r="AV12">
+        <v>2.5</v>
+      </c>
+      <c r="AW12">
+        <v>1.97</v>
+      </c>
+      <c r="AX12">
+        <v>1.61</v>
+      </c>
+      <c r="AY12">
+        <v>1.38</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
         <v>1.68</v>
       </c>
-      <c r="AS12">
-        <v>2.07</v>
-      </c>
-      <c r="AT12">
-        <v>2.55</v>
-      </c>
-      <c r="AU12">
-        <v>3.55</v>
-      </c>
-      <c r="AV12">
-        <v>2.55</v>
-      </c>
-      <c r="AW12">
-        <v>2.02</v>
-      </c>
-      <c r="AX12">
-        <v>1.66</v>
-      </c>
-      <c r="AY12">
-        <v>1.44</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.42</v>
-      </c>
       <c r="BC12">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="BD12" s="3">
         <v>45807.58333333334</v>
@@ -2944,10 +2953,10 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
         <v>107</v>
@@ -2968,127 +2977,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L13">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="M13">
-        <v>5.9</v>
+        <v>4.85</v>
       </c>
       <c r="N13">
-        <v>8.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="P13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q13">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
         <v>1.22</v>
       </c>
       <c r="S13">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T13">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="U13">
         <v>1.73</v>
       </c>
       <c r="V13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W13">
         <v>1.2</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="Z13">
         <v>1.11</v>
       </c>
       <c r="AA13">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AB13">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AC13">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AD13">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE13">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.52</v>
       </c>
       <c r="AG13">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AH13">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AI13">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AJ13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL13">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AM13">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AN13">
-        <v>4.45</v>
+        <v>2.6</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3097,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="BC13">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="BD13" s="3">
         <v>45807.58333333334</v>
@@ -3138,128 +3147,128 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="P14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="R14">
+        <v>1.29</v>
+      </c>
+      <c r="S14">
+        <v>3.25</v>
+      </c>
+      <c r="T14">
+        <v>2.3</v>
+      </c>
+      <c r="U14">
+        <v>1.53</v>
+      </c>
+      <c r="V14">
+        <v>5.25</v>
+      </c>
+      <c r="W14">
+        <v>1.13</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>10</v>
+      </c>
+      <c r="Z14">
         <v>1.2</v>
       </c>
-      <c r="S14">
-        <v>4.1</v>
-      </c>
-      <c r="T14">
-        <v>1.9</v>
-      </c>
-      <c r="U14">
-        <v>1.78</v>
-      </c>
-      <c r="V14">
-        <v>3.9</v>
-      </c>
-      <c r="W14">
-        <v>1.22</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>17</v>
-      </c>
-      <c r="Z14">
-        <v>1.11</v>
-      </c>
       <c r="AA14">
-        <v>6.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB14">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC14">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD14">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AE14">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AF14">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AG14">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AH14">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AI14">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AJ14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL14">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AM14">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AN14">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
+        <v>1.38</v>
+      </c>
+      <c r="AQ14">
+        <v>1.65</v>
+      </c>
+      <c r="AR14">
+        <v>2.02</v>
+      </c>
+      <c r="AS14">
+        <v>2.55</v>
+      </c>
+      <c r="AT14">
+        <v>3.4</v>
+      </c>
+      <c r="AU14">
+        <v>2.75</v>
+      </c>
+      <c r="AV14">
+        <v>2.08</v>
+      </c>
+      <c r="AW14">
+        <v>1.68</v>
+      </c>
+      <c r="AX14">
+        <v>1.44</v>
+      </c>
+      <c r="AY14">
         <v>1.26</v>
       </c>
-      <c r="AQ14">
-        <v>1.46</v>
-      </c>
-      <c r="AR14">
-        <v>1.73</v>
-      </c>
-      <c r="AS14">
-        <v>2.15</v>
-      </c>
-      <c r="AT14">
-        <v>2.7</v>
-      </c>
-      <c r="AU14">
-        <v>3.4</v>
-      </c>
-      <c r="AV14">
-        <v>2.5</v>
-      </c>
-      <c r="AW14">
-        <v>1.97</v>
-      </c>
-      <c r="AX14">
-        <v>1.61</v>
-      </c>
-      <c r="AY14">
-        <v>1.38</v>
-      </c>
       <c r="AZ14">
         <v>0</v>
       </c>
@@ -3267,10 +3276,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="BC14">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="BD14" s="3">
         <v>45807.58333333334</v>
@@ -3284,7 +3293,7 @@
         <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>95</v>
@@ -3308,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15">
         <v>2.33</v>
@@ -3383,10 +3392,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL15">
         <v>1.4</v>
@@ -3454,7 +3463,7 @@
         <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>95</v>
@@ -3478,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L16">
         <v>2.42</v>
@@ -3502,31 +3511,31 @@
         <v>1.38</v>
       </c>
       <c r="S16">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
         <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA16">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="AB16">
         <v>1.92</v>
@@ -3538,67 +3547,67 @@
         <v>3.22</v>
       </c>
       <c r="AE16">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
         <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH16">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AI16">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK16" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL16">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AM16">
         <v>1.31</v>
       </c>
       <c r="AN16">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AQ16">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AS16">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AT16">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AU16">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AV16">
-        <v>3.02</v>
+        <v>2.78</v>
       </c>
       <c r="AW16">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AX16">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AY16">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3624,10 +3633,10 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
         <v>111</v>
@@ -3648,127 +3657,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L17">
-        <v>2.78</v>
+        <v>1.2</v>
       </c>
       <c r="M17">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="N17">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="P17">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q17">
-        <v>1.9</v>
+        <v>4.75</v>
       </c>
       <c r="R17">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S17">
+        <v>3.56</v>
+      </c>
+      <c r="T17">
+        <v>2.11</v>
+      </c>
+      <c r="U17">
+        <v>1.72</v>
+      </c>
+      <c r="V17">
+        <v>3.9</v>
+      </c>
+      <c r="W17">
+        <v>1.14</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>21</v>
+      </c>
+      <c r="Z17">
+        <v>1.11</v>
+      </c>
+      <c r="AA17">
+        <v>5.25</v>
+      </c>
+      <c r="AB17">
+        <v>1.37</v>
+      </c>
+      <c r="AC17">
+        <v>2.85</v>
+      </c>
+      <c r="AD17">
+        <v>1.94</v>
+      </c>
+      <c r="AE17">
+        <v>1.76</v>
+      </c>
+      <c r="AF17">
+        <v>1.91</v>
+      </c>
+      <c r="AG17">
+        <v>1.85</v>
+      </c>
+      <c r="AH17">
         <v>3.25</v>
       </c>
-      <c r="T17">
-        <v>2.3</v>
-      </c>
-      <c r="U17">
-        <v>1.53</v>
-      </c>
-      <c r="V17">
-        <v>5.25</v>
-      </c>
-      <c r="W17">
-        <v>1.13</v>
-      </c>
-      <c r="X17">
+      <c r="AI17">
+        <v>1.27</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>173</v>
+      </c>
+      <c r="AL17">
         <v>1.04</v>
       </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>1.2</v>
-      </c>
-      <c r="AA17">
-        <v>4.33</v>
-      </c>
-      <c r="AB17">
-        <v>1.62</v>
-      </c>
-      <c r="AC17">
-        <v>2.25</v>
-      </c>
-      <c r="AD17">
-        <v>2.55</v>
-      </c>
-      <c r="AE17">
-        <v>1.5</v>
-      </c>
-      <c r="AF17">
-        <v>1.52</v>
-      </c>
-      <c r="AG17">
-        <v>2.35</v>
-      </c>
-      <c r="AH17">
-        <v>4.33</v>
-      </c>
-      <c r="AI17">
-        <v>1.2</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL17">
-        <v>1.51</v>
-      </c>
       <c r="AM17">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AN17">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3777,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="BC17">
-        <v>1.9</v>
+        <v>4.75</v>
       </c>
       <c r="BD17" s="3">
         <v>45807.58333333334</v>
@@ -3818,94 +3827,94 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AO18">
         <v>-1</v>
@@ -3914,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -3929,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW18">
         <v>0</v>
@@ -3947,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC18">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BD18" s="3">
         <v>45807.625</v>
@@ -3988,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L19">
         <v>1.81</v>
@@ -4063,10 +4072,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK19" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL19">
         <v>1.27</v>
@@ -4158,127 +4167,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L20">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="M20">
-        <v>3.51</v>
+        <v>3.76</v>
       </c>
       <c r="N20">
-        <v>3.83</v>
+        <v>4.5</v>
       </c>
       <c r="O20">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S20">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="T20">
         <v>2.62</v>
       </c>
       <c r="U20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AA20">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC20">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AD20">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="AE20">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AI20">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN20">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AR20">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AS20">
         <v>2.1</v>
       </c>
       <c r="AT20">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AV20">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AW20">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AX20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AY20">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4287,10 +4296,10 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BC20">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="BD20" s="3">
         <v>45807.65625</v>
@@ -4328,127 +4337,127 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21">
-        <v>2.47</v>
+        <v>3.76</v>
       </c>
       <c r="M21">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="N21">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="O21">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="P21">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q21">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="R21">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V21">
         <v>7.5</v>
       </c>
       <c r="W21">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z21">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AA21">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD21">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH21">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AI21">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK21" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL21">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AM21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN21">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ21">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AR21">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AS21">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AT21">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AU21">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AV21">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AW21">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AX21">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AY21">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4457,10 +4466,10 @@
         <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="BC21">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="BD21" s="3">
         <v>45807.65625</v>
@@ -4498,127 +4507,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L22">
+        <v>2.47</v>
+      </c>
+      <c r="M22">
+        <v>3.02</v>
+      </c>
+      <c r="N22">
+        <v>2.6</v>
+      </c>
+      <c r="O22">
+        <v>1.91</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>2.2</v>
+      </c>
+      <c r="R22">
+        <v>1.53</v>
+      </c>
+      <c r="S22">
         <v>2.51</v>
       </c>
-      <c r="M22">
-        <v>3.06</v>
-      </c>
-      <c r="N22">
-        <v>2.53</v>
-      </c>
-      <c r="O22">
+      <c r="T22">
+        <v>3.48</v>
+      </c>
+      <c r="U22">
+        <v>1.29</v>
+      </c>
+      <c r="V22">
+        <v>8.4</v>
+      </c>
+      <c r="W22">
+        <v>1.01</v>
+      </c>
+      <c r="X22">
+        <v>1.1</v>
+      </c>
+      <c r="Y22">
+        <v>7</v>
+      </c>
+      <c r="Z22">
+        <v>1.42</v>
+      </c>
+      <c r="AA22">
+        <v>2.6</v>
+      </c>
+      <c r="AB22">
+        <v>2.25</v>
+      </c>
+      <c r="AC22">
+        <v>1.53</v>
+      </c>
+      <c r="AD22">
+        <v>4.75</v>
+      </c>
+      <c r="AE22">
+        <v>1.18</v>
+      </c>
+      <c r="AF22">
         <v>2</v>
       </c>
-      <c r="P22">
-        <v>8</v>
-      </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22">
-        <v>1.4</v>
-      </c>
-      <c r="S22">
-        <v>2.62</v>
-      </c>
-      <c r="T22">
-        <v>3.13</v>
-      </c>
-      <c r="U22">
-        <v>1.33</v>
-      </c>
-      <c r="V22">
-        <v>8.5</v>
-      </c>
-      <c r="W22">
-        <v>1.06</v>
-      </c>
-      <c r="X22">
-        <v>1.07</v>
-      </c>
-      <c r="Y22">
-        <v>7.75</v>
-      </c>
-      <c r="Z22">
+      <c r="AG22">
+        <v>1.71</v>
+      </c>
+      <c r="AH22">
+        <v>9</v>
+      </c>
+      <c r="AI22">
+        <v>1.01</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>173</v>
+      </c>
+      <c r="AL22">
         <v>1.36</v>
-      </c>
-      <c r="AA22">
-        <v>2.95</v>
-      </c>
-      <c r="AB22">
-        <v>2.05</v>
-      </c>
-      <c r="AC22">
-        <v>1.65</v>
-      </c>
-      <c r="AD22">
-        <v>4.2</v>
-      </c>
-      <c r="AE22">
-        <v>1.24</v>
-      </c>
-      <c r="AF22">
-        <v>1.82</v>
-      </c>
-      <c r="AG22">
-        <v>1.85</v>
-      </c>
-      <c r="AH22">
-        <v>8</v>
-      </c>
-      <c r="AI22">
-        <v>1.07</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK22" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL22">
-        <v>1.32</v>
       </c>
       <c r="AM22">
         <v>1.3</v>
       </c>
       <c r="AN22">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ22">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AR22">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="AS22">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="AT22">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="AU22">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AV22">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AW22">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AX22">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AY22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4627,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BC22">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BD22" s="3">
         <v>45807.65625</v>
@@ -4668,127 +4677,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L23">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="M23">
-        <v>3.11</v>
+        <v>3.47</v>
       </c>
       <c r="N23">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="O23">
         <v>2.75</v>
       </c>
       <c r="P23">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="R23">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="S23">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="U23">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="V23">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W23">
+        <v>1.09</v>
+      </c>
+      <c r="X23">
         <v>1.01</v>
       </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
       <c r="Y23">
-        <v>8.1</v>
+        <v>11</v>
       </c>
       <c r="Z23">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="AA23">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AB23">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AC23">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AD23">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="AE23">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AF23">
+        <v>1.7</v>
+      </c>
+      <c r="AG23">
         <v>2</v>
       </c>
-      <c r="AG23">
-        <v>1.67</v>
-      </c>
       <c r="AH23">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="AI23">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AJ23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AM23">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AQ23">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AR23">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AS23">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT23">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AU23">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AV23">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AW23">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AX23">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AY23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4800,7 +4809,7 @@
         <v>2.75</v>
       </c>
       <c r="BC23">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BD23" s="3">
         <v>45807.65625</v>
@@ -4814,7 +4823,7 @@
         <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
         <v>95</v>
@@ -4838,127 +4847,127 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24">
-        <v>5.7</v>
+        <v>2.51</v>
       </c>
       <c r="M24">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="N24">
-        <v>1.47</v>
+        <v>2.53</v>
       </c>
       <c r="O24">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="P24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q24">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="R24">
+        <v>1.41</v>
+      </c>
+      <c r="S24">
+        <v>2.62</v>
+      </c>
+      <c r="T24">
+        <v>2.9</v>
+      </c>
+      <c r="U24">
+        <v>1.31</v>
+      </c>
+      <c r="V24">
+        <v>8.5</v>
+      </c>
+      <c r="W24">
+        <v>1.01</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>8</v>
+      </c>
+      <c r="Z24">
+        <v>1.38</v>
+      </c>
+      <c r="AA24">
+        <v>3</v>
+      </c>
+      <c r="AB24">
+        <v>2.05</v>
+      </c>
+      <c r="AC24">
+        <v>1.65</v>
+      </c>
+      <c r="AD24">
+        <v>3.9</v>
+      </c>
+      <c r="AE24">
+        <v>1.21</v>
+      </c>
+      <c r="AF24">
+        <v>1.85</v>
+      </c>
+      <c r="AG24">
+        <v>1.83</v>
+      </c>
+      <c r="AH24">
+        <v>8.1</v>
+      </c>
+      <c r="AI24">
+        <v>1.07</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>173</v>
+      </c>
+      <c r="AL24">
         <v>1.32</v>
       </c>
-      <c r="S24">
-        <v>2.95</v>
-      </c>
-      <c r="T24">
-        <v>2.55</v>
-      </c>
-      <c r="U24">
-        <v>1.44</v>
-      </c>
-      <c r="V24">
-        <v>5.75</v>
-      </c>
-      <c r="W24">
-        <v>1.09</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>10</v>
-      </c>
-      <c r="Z24">
-        <v>1.17</v>
-      </c>
-      <c r="AA24">
-        <v>3.6</v>
-      </c>
-      <c r="AB24">
-        <v>1.75</v>
-      </c>
-      <c r="AC24">
-        <v>1.91</v>
-      </c>
-      <c r="AD24">
-        <v>3.1</v>
-      </c>
-      <c r="AE24">
-        <v>1.36</v>
-      </c>
-      <c r="AF24">
-        <v>1.83</v>
-      </c>
-      <c r="AG24">
-        <v>1.8</v>
-      </c>
-      <c r="AH24">
-        <v>4.7</v>
-      </c>
-      <c r="AI24">
-        <v>1.12</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL24">
-        <v>1.18</v>
-      </c>
       <c r="AM24">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN24">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="AO24">
         <v>-1</v>
       </c>
       <c r="AP24">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AR24">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AS24">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AT24">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AU24">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="AV24">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AW24">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AX24">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AY24">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24">
         <v>0</v>
@@ -4967,10 +4976,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="BC24">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="BD24" s="3">
         <v>45807.65625</v>
@@ -5008,127 +5017,127 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25">
-        <v>1.8</v>
+        <v>5.7</v>
       </c>
       <c r="M25">
-        <v>3.47</v>
+        <v>4.1</v>
       </c>
       <c r="N25">
-        <v>3.88</v>
+        <v>1.47</v>
       </c>
       <c r="O25">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="R25">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S25">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T25">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U25">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>7.75</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AA25">
-        <v>2.85</v>
+        <v>3.6</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AD25">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="AE25">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG25">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AH25">
-        <v>7</v>
+        <v>4.35</v>
       </c>
       <c r="AI25">
+        <v>1.14</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>173</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>173</v>
+      </c>
+      <c r="AL25">
+        <v>1.2</v>
+      </c>
+      <c r="AM25">
+        <v>1.2</v>
+      </c>
+      <c r="AN25">
         <v>1.08</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK25" t="s">
-        <v>171</v>
-      </c>
-      <c r="AL25">
-        <v>1.33</v>
-      </c>
-      <c r="AM25">
-        <v>1.25</v>
-      </c>
-      <c r="AN25">
-        <v>1.93</v>
       </c>
       <c r="AO25">
         <v>-1</v>
       </c>
       <c r="AP25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AR25">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AS25">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AT25">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AU25">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AV25">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AW25">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AX25">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AY25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AZ25">
         <v>0</v>
@@ -5137,10 +5146,10 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="BC25">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="BD25" s="3">
         <v>45807.65625</v>
@@ -5178,124 +5187,124 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="M26">
-        <v>3.76</v>
+        <v>3.51</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>3.83</v>
       </c>
       <c r="O26">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R26">
+        <v>1.36</v>
+      </c>
+      <c r="S26">
+        <v>2.9</v>
+      </c>
+      <c r="T26">
+        <v>2.72</v>
+      </c>
+      <c r="U26">
+        <v>1.42</v>
+      </c>
+      <c r="V26">
+        <v>6</v>
+      </c>
+      <c r="W26">
+        <v>1.09</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z26">
+        <v>1.27</v>
+      </c>
+      <c r="AA26">
+        <v>3.58</v>
+      </c>
+      <c r="AB26">
+        <v>1.83</v>
+      </c>
+      <c r="AC26">
+        <v>1.87</v>
+      </c>
+      <c r="AD26">
+        <v>3.08</v>
+      </c>
+      <c r="AE26">
         <v>1.33</v>
       </c>
-      <c r="S26">
-        <v>3.16</v>
-      </c>
-      <c r="T26">
-        <v>2.5</v>
-      </c>
-      <c r="U26">
-        <v>1.47</v>
-      </c>
-      <c r="V26">
-        <v>5.5</v>
-      </c>
-      <c r="W26">
-        <v>1.11</v>
-      </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>12</v>
-      </c>
-      <c r="Z26">
-        <v>1.18</v>
-      </c>
-      <c r="AA26">
-        <v>3.8</v>
-      </c>
-      <c r="AB26">
-        <v>1.7</v>
-      </c>
-      <c r="AC26">
-        <v>1.95</v>
-      </c>
-      <c r="AD26">
-        <v>2.88</v>
-      </c>
-      <c r="AE26">
-        <v>1.38</v>
-      </c>
       <c r="AF26">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
         <v>2</v>
       </c>
       <c r="AH26">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AI26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL26">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM26">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AR26">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS26">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AT26">
         <v>2.74</v>
       </c>
       <c r="AU26">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="AV26">
         <v>2.7</v>
       </c>
       <c r="AW26">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AX26">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AY26">
         <v>1.35</v>
@@ -5307,10 +5316,10 @@
         <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BC26">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="BD26" s="3">
         <v>45807.65625</v>
@@ -5348,127 +5357,127 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L27">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="M27">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="O27">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="P27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
+        <v>1.41</v>
+      </c>
+      <c r="S27">
+        <v>2.55</v>
+      </c>
+      <c r="T27">
+        <v>2.88</v>
+      </c>
+      <c r="U27">
         <v>1.35</v>
       </c>
-      <c r="S27">
-        <v>3.2</v>
-      </c>
-      <c r="T27">
-        <v>2.57</v>
-      </c>
-      <c r="U27">
-        <v>1.44</v>
-      </c>
       <c r="V27">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>9.75</v>
+        <v>7</v>
       </c>
       <c r="Z27">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA27">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AB27">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD27">
-        <v>2.74</v>
+        <v>3.7</v>
       </c>
       <c r="AE27">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AF27">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH27">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AI27">
         <v>1.06</v>
       </c>
       <c r="AJ27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK27" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL27">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AM27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AN27">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="AR27">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="AS27">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="AT27">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="AU27">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AV27">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="AW27">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AX27">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AY27">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5477,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BC27">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="BD27" s="3">
         <v>45807.65625</v>
@@ -5494,7 +5503,7 @@
         <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
         <v>95</v>
@@ -5518,94 +5527,94 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28">
-        <v>3.78</v>
+        <v>1.74</v>
       </c>
       <c r="M28">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N28">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="O28">
+        <v>1.5</v>
+      </c>
+      <c r="P28">
+        <v>9</v>
+      </c>
+      <c r="Q28">
         <v>2.75</v>
       </c>
-      <c r="P28">
-        <v>9.5</v>
-      </c>
-      <c r="Q28">
-        <v>1.53</v>
-      </c>
       <c r="R28">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T28">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="U28">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V28">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X28">
         <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z28">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AA28">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AB28">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC28">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD28">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="AE28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF28">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG28">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AH28">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AJ28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL28">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AM28">
         <v>1.22</v>
       </c>
       <c r="AN28">
-        <v>1.22</v>
+        <v>2.15</v>
       </c>
       <c r="AO28">
         <v>-1</v>
@@ -5614,31 +5623,31 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AR28">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AS28">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AT28">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="AU28">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AV28">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AW28">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AX28">
-        <v>1.67</v>
+        <v>1.47</v>
       </c>
       <c r="AY28">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AZ28">
         <v>0</v>
@@ -5647,10 +5656,10 @@
         <v>0</v>
       </c>
       <c r="BB28">
+        <v>1.5</v>
+      </c>
+      <c r="BC28">
         <v>2.75</v>
-      </c>
-      <c r="BC28">
-        <v>1.53</v>
       </c>
       <c r="BD28" s="3">
         <v>45807.65625</v>
@@ -5688,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L29">
         <v>1.5</v>
@@ -5709,34 +5718,34 @@
         <v>3.5</v>
       </c>
       <c r="R29">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S29">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="T29">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="U29">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V29">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>9.65</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z29">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AA29">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB29">
         <v>1.94</v>
@@ -5745,31 +5754,31 @@
         <v>1.76</v>
       </c>
       <c r="AD29">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF29">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AH29">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AI29">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AJ29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL29">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AM29">
         <v>1.2</v>
@@ -5781,7 +5790,7 @@
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29">
         <v>1.48</v>
@@ -5790,7 +5799,7 @@
         <v>1.75</v>
       </c>
       <c r="AS29">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AT29">
         <v>2.8</v>
@@ -5799,7 +5808,7 @@
         <v>3.4</v>
       </c>
       <c r="AV29">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="AW29">
         <v>1.95</v>
@@ -5808,7 +5817,7 @@
         <v>1.6</v>
       </c>
       <c r="AY29">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5858,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L30">
         <v>2.37</v>
@@ -5879,25 +5888,25 @@
         <v>2.3</v>
       </c>
       <c r="R30">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S30">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U30">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V30">
         <v>8.9</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
         <v>7</v>
@@ -5906,7 +5915,7 @@
         <v>1.4</v>
       </c>
       <c r="AA30">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AB30">
         <v>2.25</v>
@@ -5915,28 +5924,28 @@
         <v>1.53</v>
       </c>
       <c r="AD30">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE30">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH30">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AI30">
         <v>1.02</v>
       </c>
       <c r="AJ30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL30">
         <v>1.35</v>
@@ -5957,7 +5966,7 @@
         <v>0</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS30">
         <v>0</v>
@@ -6028,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L31">
         <v>3.5</v>
@@ -6049,16 +6058,16 @@
         <v>1.83</v>
       </c>
       <c r="R31">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S31">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="U31">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V31">
         <v>8.800000000000001</v>
@@ -6067,10 +6076,10 @@
         <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>6.8</v>
+        <v>6.25</v>
       </c>
       <c r="Z31">
         <v>1.48</v>
@@ -6085,37 +6094,37 @@
         <v>1.49</v>
       </c>
       <c r="AD31">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AE31">
         <v>1.15</v>
       </c>
       <c r="AF31">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AG31">
         <v>1.7</v>
       </c>
       <c r="AH31">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AI31">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL31">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AM31">
         <v>1.36</v>
       </c>
       <c r="AN31">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AO31">
         <v>-1</v>
@@ -6124,31 +6133,31 @@
         <v>1.5</v>
       </c>
       <c r="AQ31">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AR31">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="AS31">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AT31">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AU31">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AV31">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AW31">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AX31">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AY31">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6198,43 +6207,43 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32">
         <v>0</v>
@@ -6243,49 +6252,49 @@
         <v>0</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL32">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AM32">
         <v>0</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO32">
         <v>-1</v>
@@ -6327,10 +6336,10 @@
         <v>0</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD32" s="3">
         <v>45807.75</v>
@@ -6368,7 +6377,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L33">
         <v>2.42</v>
@@ -6389,19 +6398,19 @@
         <v>2.2</v>
       </c>
       <c r="R33">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S33">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U33">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V33">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
       <c r="W33">
         <v>1.02</v>
@@ -6425,70 +6434,70 @@
         <v>1.48</v>
       </c>
       <c r="AD33">
-        <v>6.2</v>
+        <v>6.25</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="AG33">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH33">
         <v>11</v>
       </c>
       <c r="AI33">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL33">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AM33">
         <v>1.37</v>
       </c>
       <c r="AN33">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AO33">
         <v>-1</v>
       </c>
       <c r="AP33">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ33">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AR33">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AS33">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AT33">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU33">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AV33">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AW33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AX33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AY33">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AZ33">
         <v>0</v>
@@ -6538,94 +6547,94 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH34">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AJ34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM34">
         <v>0</v>
       </c>
       <c r="AN34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO34">
         <v>-1</v>
@@ -6667,10 +6676,10 @@
         <v>0</v>
       </c>
       <c r="BB34">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BC34">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD34" s="3">
         <v>45807.83333333334</v>
@@ -6708,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L35">
         <v>1.96</v>
@@ -6729,40 +6738,40 @@
         <v>2.63</v>
       </c>
       <c r="R35">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S35">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U35">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V35">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>6.2</v>
+        <v>9.1</v>
       </c>
       <c r="Z35">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AA35">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AB35">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AD35">
         <v>3.8</v>
@@ -6771,31 +6780,31 @@
         <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG35">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH35">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AI35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AJ35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL35">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AM35">
         <v>1.28</v>
       </c>
       <c r="AN35">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AO35">
         <v>-1</v>
@@ -6878,94 +6887,94 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM36">
         <v>0</v>
       </c>
       <c r="AN36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO36">
         <v>-1</v>
@@ -7007,10 +7016,10 @@
         <v>0</v>
       </c>
       <c r="BB36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BC36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD36" s="3">
         <v>45807.89583333334</v>
@@ -7048,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L37">
         <v>2.24</v>
@@ -7069,28 +7078,28 @@
         <v>2.63</v>
       </c>
       <c r="R37">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S37">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="T37">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U37">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="V37">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="W37">
         <v>1</v>
       </c>
       <c r="X37">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Z37">
         <v>1.74</v>
@@ -7099,76 +7108,76 @@
         <v>1.96</v>
       </c>
       <c r="AB37">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AC37">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD37">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE37">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG37">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AH37">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AI37">
         <v>1.01</v>
       </c>
       <c r="AJ37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK37" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL37">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AM37">
         <v>1.39</v>
       </c>
       <c r="AN37">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AO37">
         <v>-1</v>
       </c>
       <c r="AP37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ37">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AR37">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="AS37">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AT37">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU37">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AV37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AW37">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AX37">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AY37">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AZ37">
         <v>0</v>
@@ -7218,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L38">
         <v>2.7</v>
@@ -7233,46 +7242,46 @@
         <v>2.2</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q38">
         <v>1.73</v>
       </c>
       <c r="R38">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S38">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="T38">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U38">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="V38">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB38">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC38">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AD38">
         <v>2.2</v>
@@ -7281,31 +7290,31 @@
         <v>1.55</v>
       </c>
       <c r="AF38">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH38">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI38">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AK38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO38">
         <v>-1</v>

--- a/jogos_2025-05-30.xlsx
+++ b/jogos_2025-05-30.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="O3" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.72</v>
+        <v>2.45</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>2.25</v>
+        <v>3.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.72</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['3', '38']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['70', '90']</t>
+          <t>['32', '55']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.68</v>
+        <v>2.23</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45807.41666666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="R4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['3', '38']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['70', '90']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.36</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AH4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.66</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['32', '55']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45807.41666666666</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.49</v>
+        <v>6.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="N7" t="n">
-        <v>2.6</v>
+        <v>1.52</v>
       </c>
       <c r="O7" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="U7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AB7" t="n">
         <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45807.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,20 +1417,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="M8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.1</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.94</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="X8" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['74', '87']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45807.5</v>
@@ -1536,29 +1536,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="M9" t="n">
-        <v>3.59</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.52</v>
+        <v>2.37</v>
       </c>
       <c r="O9" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.91</v>
+        <v>2.94</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['74', '87']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.44</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AI9" t="n">
-        <v>3.46</v>
+        <v>1.82</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45807.5</v>
@@ -1794,32 +1794,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="M11" t="n">
-        <v>4.63</v>
+        <v>3.22</v>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>5.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>2.51</v>
       </c>
       <c r="P11" t="n">
-        <v>2.71</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.53</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['23', '62', '77', '83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.78</v>
+        <v>2.3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45807.54166666666</v>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.74</v>
+        <v>1.23</v>
       </c>
       <c r="M13" t="n">
-        <v>3.22</v>
+        <v>4.63</v>
       </c>
       <c r="N13" t="n">
-        <v>5.01</v>
+        <v>9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>2.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['23', '62', '77', '83']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45807.54166666666</v>
@@ -2191,63 +2191,63 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="M14" t="n">
-        <v>4.85</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
         <v>1.9</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.98</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
         <v>1.11</v>
@@ -2256,44 +2256,44 @@
         <v>6.25</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
         <v>3.1</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AC14" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['17', '81']</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '90+2']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45807.58333333334</v>
@@ -2329,94 +2329,94 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['6', '27', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['69', '75', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,32 +2439,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['55', '57']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45807.58333333334</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,37 +2604,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.97</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
         <v>1.11</v>
@@ -2643,44 +2643,44 @@
         <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
         <v>3.1</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.9</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['17', '81']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>2.9</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['33', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.15</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45807.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.17</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>3.38</v>
       </c>
       <c r="N18" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.46</v>
+        <v>3.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2.81</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.24</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="X18" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['54', '60', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.17</v>
+        <v>2.02</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.75</v>
+        <v>2.04</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45807.58333333334</v>
@@ -2826,119 +2826,119 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['54', '60', '90+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['55', '57']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>3.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.9</v>
+        <v>4.75</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45807.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.78</v>
+        <v>1.81</v>
       </c>
       <c r="M23" t="n">
-        <v>3.47</v>
+        <v>3.51</v>
       </c>
       <c r="N23" t="n">
-        <v>1.76</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.53</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T23" t="n">
         <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>['45', '52']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['10']</t>
         </is>
       </c>
       <c r="AG23" t="n">
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45807.65625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.06</v>
+        <v>3.47</v>
       </c>
       <c r="N24" t="n">
-        <v>2.53</v>
+        <v>3.88</v>
       </c>
       <c r="O24" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>4.07</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
         <v>1.37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['19', '81']</t>
+          <t>['54', '75']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['23', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45807.65625</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
         <v>3</v>
       </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,31 +3636,31 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.74</v>
+        <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>1.47</v>
       </c>
       <c r="O25" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="U25" t="n">
         <v>1.5</v>
@@ -3669,50 +3669,50 @@
         <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AB25" t="n">
         <v>1.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['26', '31', '82']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45807.65625</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.63</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
-        <v>3.76</v>
+        <v>3.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.5</v>
+        <v>2.53</v>
       </c>
       <c r="O26" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.33</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA26" t="n">
         <v>3.6</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3</v>
-      </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['4', '53']</t>
+          <t>['19', '81']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['23', '90+3']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45807.65625</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.7</v>
+        <v>3.78</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB27" t="n">
         <v>1.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45807.65625</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="M29" t="n">
-        <v>3.47</v>
+        <v>3.64</v>
       </c>
       <c r="N29" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['54', '75']</t>
+          <t>['26', '31', '82']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45807.65625</v>
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -4281,31 +4281,31 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.81</v>
+        <v>1.63</v>
       </c>
       <c r="M30" t="n">
-        <v>3.51</v>
+        <v>3.76</v>
       </c>
       <c r="N30" t="n">
-        <v>3.83</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
         <v>2.95</v>
       </c>
       <c r="T30" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="U30" t="n">
         <v>1.42</v>
@@ -4314,50 +4314,50 @@
         <v>1.05</v>
       </c>
       <c r="W30" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X30" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD30" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['45', '52']</t>
+          <t>['4', '53']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45807.65625</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>3.64</v>
       </c>
       <c r="N31" t="n">
-        <v>2.71</v>
+        <v>5.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH31" t="n">
         <v>2.45</v>
       </c>
-      <c r="T31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['19', '63', '68']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AI31" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45807.66666666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="M32" t="n">
-        <v>3.64</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>5.6</v>
+        <v>2.71</v>
       </c>
       <c r="O32" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['19', '63', '68']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>3.5</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45807.66666666666</v>
